--- a/book/output/Risk_Identification_Template_Pack.xlsx
+++ b/book/output/Risk_Identification_Template_Pack.xlsx
@@ -37,8 +37,11 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="27. Audit Programme" sheetId="28" state="visible" r:id="rId28"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="28. Reg Traceability" sheetId="29" state="visible" r:id="rId29"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="29. Lessons Learned" sheetId="30" state="visible" r:id="rId30"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="30. Industry Loss DB" sheetId="31" state="visible" r:id="rId31"/>
   </sheets>
-  <definedNames/>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="30" hidden="1">'30. Industry Loss DB'!$A$5:$I$184</definedName>
+  </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
@@ -147,7 +150,7 @@
       <sz val="10"/>
     </font>
   </fonts>
-  <fills count="6">
+  <fills count="7">
     <fill>
       <patternFill/>
     </fill>
@@ -178,6 +181,12 @@
         <bgColor rgb="00E8E8E8"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00F5F5F5"/>
+        <bgColor rgb="00F5F5F5"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="2">
     <border>
@@ -205,7 +214,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="34">
+  <cellXfs count="38">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -263,6 +272,18 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="3" fontId="5" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="3" fontId="5" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -630,7 +651,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A2:A24"/>
+  <dimension ref="A2:A25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="80" customWidth="1" min="1" max="1"/>
@@ -758,7 +779,14 @@
     <row r="24">
       <c r="A24" s="5" t="inlineStr">
         <is>
-          <t>6. See the book chapter references on each tab for methodology context.</t>
+          <t>6. Tab 30 (Industry Loss Database) contains 179 historical bank failures — use it for taxonomy testing and calibration.</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="5" t="inlineStr">
+        <is>
+          <t>7. See the book chapter references on each tab for methodology context.</t>
         </is>
       </c>
     </row>
@@ -9033,6 +9061,7440 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet31.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <tabColor rgb="001B2A4A"/>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:I184"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="6" customWidth="1" min="1" max="1"/>
+    <col width="38" customWidth="1" min="2" max="2"/>
+    <col width="22" customWidth="1" min="3" max="3"/>
+    <col width="8" customWidth="1" min="4" max="4"/>
+    <col width="50" customWidth="1" min="5" max="5"/>
+    <col width="18" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="7" max="7"/>
+    <col width="24" customWidth="1" min="8" max="8"/>
+    <col width="14" customWidth="1" min="9" max="9"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="12" t="inlineStr">
+        <is>
+          <t>Industry Loss Database (179 Events)</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="13" t="inlineStr">
+        <is>
+          <t>Book Reference: Chapter 16, Appendix A — Empirical foundation for the methodology</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="14" t="inlineStr">
+        <is>
+          <t>179 bank and financial institution loss events spanning 35 countries and six decades. Use Excel auto-filter to sort and filter by any column. USD ($M) column enables numeric sorting by loss magnitude.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="15" t="inlineStr">
+        <is>
+          <t>#</t>
+        </is>
+      </c>
+      <c r="B5" s="15" t="inlineStr">
+        <is>
+          <t>Institution</t>
+        </is>
+      </c>
+      <c r="C5" s="15" t="inlineStr">
+        <is>
+          <t>Country</t>
+        </is>
+      </c>
+      <c r="D5" s="15" t="inlineStr">
+        <is>
+          <t>Year</t>
+        </is>
+      </c>
+      <c r="E5" s="15" t="inlineStr">
+        <is>
+          <t>Risk Event</t>
+        </is>
+      </c>
+      <c r="F5" s="15" t="inlineStr">
+        <is>
+          <t>L1 Category</t>
+        </is>
+      </c>
+      <c r="G5" s="15" t="inlineStr">
+        <is>
+          <t>COSO</t>
+        </is>
+      </c>
+      <c r="H5" s="15" t="inlineStr">
+        <is>
+          <t>Est. Loss (Original)</t>
+        </is>
+      </c>
+      <c r="I5" s="15" t="inlineStr">
+        <is>
+          <t>USD ($M)</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="23" t="n">
+        <v>1</v>
+      </c>
+      <c r="B6" s="16" t="inlineStr">
+        <is>
+          <t>Malaysia Development Berhad (Malaysia)</t>
+        </is>
+      </c>
+      <c r="C6" s="16" t="inlineStr">
+        <is>
+          <t>Malaysia</t>
+        </is>
+      </c>
+      <c r="D6" s="23" t="n">
+        <v>2015</v>
+      </c>
+      <c r="E6" s="16" t="inlineStr">
+        <is>
+          <t>Fraud and Money Laundering</t>
+        </is>
+      </c>
+      <c r="F6" s="16" t="inlineStr">
+        <is>
+          <t>Operational Risk</t>
+        </is>
+      </c>
+      <c r="G6" s="16" t="inlineStr">
+        <is>
+          <t>Compliance</t>
+        </is>
+      </c>
+      <c r="H6" s="16" t="inlineStr">
+        <is>
+          <t>$4.5 billion</t>
+        </is>
+      </c>
+      <c r="I6" s="34" t="n">
+        <v>4500</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="35" t="n">
+        <v>2</v>
+      </c>
+      <c r="B7" s="36" t="inlineStr">
+        <is>
+          <t>Adelphia Communications</t>
+        </is>
+      </c>
+      <c r="C7" s="36" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="D7" s="35" t="n">
+        <v>2002</v>
+      </c>
+      <c r="E7" s="36" t="inlineStr">
+        <is>
+          <t>Internal Corporate Fraud</t>
+        </is>
+      </c>
+      <c r="F7" s="36" t="inlineStr">
+        <is>
+          <t>Operational Risk</t>
+        </is>
+      </c>
+      <c r="G7" s="36" t="inlineStr">
+        <is>
+          <t>Reporting</t>
+        </is>
+      </c>
+      <c r="H7" s="36" t="inlineStr">
+        <is>
+          <t>$2.5 billion</t>
+        </is>
+      </c>
+      <c r="I7" s="37" t="n">
+        <v>2500</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="23" t="n">
+        <v>3</v>
+      </c>
+      <c r="B8" s="16" t="inlineStr">
+        <is>
+          <t>AIG (US)</t>
+        </is>
+      </c>
+      <c r="C8" s="16" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="D8" s="23" t="n">
+        <v>2008</v>
+      </c>
+      <c r="E8" s="16" t="inlineStr">
+        <is>
+          <t>Overexposure to Credit Default Swaps leading to liquidity crisis</t>
+        </is>
+      </c>
+      <c r="F8" s="16" t="inlineStr">
+        <is>
+          <t>Credit Risk</t>
+        </is>
+      </c>
+      <c r="G8" s="16" t="inlineStr">
+        <is>
+          <t>Strategic</t>
+        </is>
+      </c>
+      <c r="H8" s="16" t="inlineStr">
+        <is>
+          <t>$85 billion</t>
+        </is>
+      </c>
+      <c r="I8" s="34" t="n">
+        <v>85000</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="35" t="n">
+        <v>4</v>
+      </c>
+      <c r="B9" s="36" t="inlineStr">
+        <is>
+          <t>Allied Irish Bank</t>
+        </is>
+      </c>
+      <c r="C9" s="36" t="inlineStr">
+        <is>
+          <t>Ireland</t>
+        </is>
+      </c>
+      <c r="D9" s="35" t="n">
+        <v>2002</v>
+      </c>
+      <c r="E9" s="36" t="inlineStr">
+        <is>
+          <t>Rogue Trader (John Rusnak)</t>
+        </is>
+      </c>
+      <c r="F9" s="36" t="inlineStr">
+        <is>
+          <t>Operational Risk</t>
+        </is>
+      </c>
+      <c r="G9" s="36" t="inlineStr">
+        <is>
+          <t>Operations</t>
+        </is>
+      </c>
+      <c r="H9" s="36" t="inlineStr">
+        <is>
+          <t>$691 million</t>
+        </is>
+      </c>
+      <c r="I9" s="37" t="n">
+        <v>691</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="23" t="n">
+        <v>5</v>
+      </c>
+      <c r="B10" s="16" t="inlineStr">
+        <is>
+          <t>Allied Irish Banks (Ireland)</t>
+        </is>
+      </c>
+      <c r="C10" s="16" t="inlineStr">
+        <is>
+          <t>Ireland</t>
+        </is>
+      </c>
+      <c r="D10" s="23" t="n">
+        <v>2008</v>
+      </c>
+      <c r="E10" s="16" t="inlineStr">
+        <is>
+          <t>Overexposure to Property Market leading to nationalization</t>
+        </is>
+      </c>
+      <c r="F10" s="16" t="inlineStr">
+        <is>
+          <t>Credit Risk</t>
+        </is>
+      </c>
+      <c r="G10" s="16" t="inlineStr">
+        <is>
+          <t>Strategic</t>
+        </is>
+      </c>
+      <c r="H10" s="16" t="inlineStr">
+        <is>
+          <t>€21 billion</t>
+        </is>
+      </c>
+      <c r="I10" s="34" t="n">
+        <v>24800</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="35" t="n">
+        <v>6</v>
+      </c>
+      <c r="B11" s="36" t="inlineStr">
+        <is>
+          <t>Alpha Bank (Greece)</t>
+        </is>
+      </c>
+      <c r="C11" s="36" t="inlineStr">
+        <is>
+          <t>Greece</t>
+        </is>
+      </c>
+      <c r="D11" s="35" t="n">
+        <v>2010</v>
+      </c>
+      <c r="E11" s="36" t="inlineStr">
+        <is>
+          <t>Overexposure to Greek Sovereign Debt</t>
+        </is>
+      </c>
+      <c r="F11" s="36" t="inlineStr">
+        <is>
+          <t>Credit Risk</t>
+        </is>
+      </c>
+      <c r="G11" s="36" t="inlineStr">
+        <is>
+          <t>Strategic</t>
+        </is>
+      </c>
+      <c r="H11" s="36" t="inlineStr">
+        <is>
+          <t>~€4 billion</t>
+        </is>
+      </c>
+      <c r="I11" s="37" t="n">
+        <v>4700</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="23" t="n">
+        <v>7</v>
+      </c>
+      <c r="B12" s="16" t="inlineStr">
+        <is>
+          <t>AmBank (Malaysia)</t>
+        </is>
+      </c>
+      <c r="C12" s="16" t="inlineStr">
+        <is>
+          <t>Malaysia</t>
+        </is>
+      </c>
+      <c r="D12" s="23" t="n">
+        <v>2015</v>
+      </c>
+      <c r="E12" s="16" t="inlineStr">
+        <is>
+          <t>Involvement in 1MDB Scandal</t>
+        </is>
+      </c>
+      <c r="F12" s="16" t="inlineStr">
+        <is>
+          <t>Conduct Risk</t>
+        </is>
+      </c>
+      <c r="G12" s="16" t="inlineStr">
+        <is>
+          <t>Compliance</t>
+        </is>
+      </c>
+      <c r="H12" s="16" t="inlineStr">
+        <is>
+          <t>$700 million</t>
+        </is>
+      </c>
+      <c r="I12" s="34" t="n">
+        <v>700</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="35" t="n">
+        <v>8</v>
+      </c>
+      <c r="B13" s="36" t="inlineStr">
+        <is>
+          <t>AMCORE Financial</t>
+        </is>
+      </c>
+      <c r="C13" s="36" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="D13" s="35" t="n">
+        <v>2010</v>
+      </c>
+      <c r="E13" s="36" t="inlineStr">
+        <is>
+          <t>Overexposure to Commercial Real Estate</t>
+        </is>
+      </c>
+      <c r="F13" s="36" t="inlineStr">
+        <is>
+          <t>Credit Risk</t>
+        </is>
+      </c>
+      <c r="G13" s="36" t="inlineStr">
+        <is>
+          <t>Strategic</t>
+        </is>
+      </c>
+      <c r="H13" s="36" t="inlineStr">
+        <is>
+          <t>$3.8 billion</t>
+        </is>
+      </c>
+      <c r="I13" s="37" t="n">
+        <v>3800</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="23" t="n">
+        <v>9</v>
+      </c>
+      <c r="B14" s="16" t="inlineStr">
+        <is>
+          <t>American International Group (AIG)</t>
+        </is>
+      </c>
+      <c r="C14" s="16" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="D14" s="23" t="n">
+        <v>2005</v>
+      </c>
+      <c r="E14" s="16" t="inlineStr">
+        <is>
+          <t>Accounting Fraud</t>
+        </is>
+      </c>
+      <c r="F14" s="16" t="inlineStr">
+        <is>
+          <t>Operational Risk</t>
+        </is>
+      </c>
+      <c r="G14" s="16" t="inlineStr">
+        <is>
+          <t>Reporting</t>
+        </is>
+      </c>
+      <c r="H14" s="16" t="inlineStr">
+        <is>
+          <t>$3.9 billion</t>
+        </is>
+      </c>
+      <c r="I14" s="34" t="n">
+        <v>3900</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="35" t="n">
+        <v>10</v>
+      </c>
+      <c r="B15" s="36" t="inlineStr">
+        <is>
+          <t>American International Group (AIG)</t>
+        </is>
+      </c>
+      <c r="C15" s="36" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="D15" s="35" t="n">
+        <v>2008</v>
+      </c>
+      <c r="E15" s="36" t="inlineStr">
+        <is>
+          <t>Overexposure to Credit Default Swaps</t>
+        </is>
+      </c>
+      <c r="F15" s="36" t="inlineStr">
+        <is>
+          <t>Credit Risk</t>
+        </is>
+      </c>
+      <c r="G15" s="36" t="inlineStr">
+        <is>
+          <t>Strategic</t>
+        </is>
+      </c>
+      <c r="H15" s="36" t="inlineStr">
+        <is>
+          <t>$85 billion</t>
+        </is>
+      </c>
+      <c r="I15" s="37" t="n">
+        <v>85000</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="23" t="n">
+        <v>11</v>
+      </c>
+      <c r="B16" s="16" t="inlineStr">
+        <is>
+          <t>American Savings &amp; Loan</t>
+        </is>
+      </c>
+      <c r="C16" s="16" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="D16" s="23" t="n">
+        <v>1988</v>
+      </c>
+      <c r="E16" s="16" t="inlineStr">
+        <is>
+          <t>High-risk Mortgage Lending and Securities Investments</t>
+        </is>
+      </c>
+      <c r="F16" s="16" t="inlineStr">
+        <is>
+          <t>Credit Risk</t>
+        </is>
+      </c>
+      <c r="G16" s="16" t="inlineStr">
+        <is>
+          <t>Strategic</t>
+        </is>
+      </c>
+      <c r="H16" s="16" t="inlineStr">
+        <is>
+          <t>$5.4 billion</t>
+        </is>
+      </c>
+      <c r="I16" s="34" t="n">
+        <v>5400</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="35" t="n">
+        <v>12</v>
+      </c>
+      <c r="B17" s="36" t="inlineStr">
+        <is>
+          <t>AMP (Australia)</t>
+        </is>
+      </c>
+      <c r="C17" s="36" t="inlineStr">
+        <is>
+          <t>Australia</t>
+        </is>
+      </c>
+      <c r="D17" s="35" t="n">
+        <v>2018</v>
+      </c>
+      <c r="E17" s="36" t="inlineStr">
+        <is>
+          <t>Fees for No Service</t>
+        </is>
+      </c>
+      <c r="F17" s="36" t="inlineStr">
+        <is>
+          <t>Conduct Risk</t>
+        </is>
+      </c>
+      <c r="G17" s="36" t="inlineStr">
+        <is>
+          <t>Compliance</t>
+        </is>
+      </c>
+      <c r="H17" s="36" t="inlineStr">
+        <is>
+          <t>AUD 600 million</t>
+        </is>
+      </c>
+      <c r="I17" s="37" t="n">
+        <v>432</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="23" t="n">
+        <v>13</v>
+      </c>
+      <c r="B18" s="16" t="inlineStr">
+        <is>
+          <t>Anglo Irish Bank</t>
+        </is>
+      </c>
+      <c r="C18" s="16" t="inlineStr">
+        <is>
+          <t>Ireland</t>
+        </is>
+      </c>
+      <c r="D18" s="23" t="n">
+        <v>2010</v>
+      </c>
+      <c r="E18" s="16" t="inlineStr">
+        <is>
+          <t>Hidden Loans and Accounting Fraud</t>
+        </is>
+      </c>
+      <c r="F18" s="16" t="inlineStr">
+        <is>
+          <t>Operational Risk</t>
+        </is>
+      </c>
+      <c r="G18" s="16" t="inlineStr">
+        <is>
+          <t>Reporting</t>
+        </is>
+      </c>
+      <c r="H18" s="16" t="inlineStr">
+        <is>
+          <t>€29.3 billion</t>
+        </is>
+      </c>
+      <c r="I18" s="34" t="n">
+        <v>34600</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="35" t="n">
+        <v>14</v>
+      </c>
+      <c r="B19" s="36" t="inlineStr">
+        <is>
+          <t>ANZ (Australia)</t>
+        </is>
+      </c>
+      <c r="C19" s="36" t="inlineStr">
+        <is>
+          <t>Australia</t>
+        </is>
+      </c>
+      <c r="D19" s="35" t="n">
+        <v>2018</v>
+      </c>
+      <c r="E19" s="36" t="inlineStr">
+        <is>
+          <t>Interest Rate Rigging</t>
+        </is>
+      </c>
+      <c r="F19" s="36" t="inlineStr">
+        <is>
+          <t>Conduct Risk</t>
+        </is>
+      </c>
+      <c r="G19" s="36" t="inlineStr">
+        <is>
+          <t>Compliance</t>
+        </is>
+      </c>
+      <c r="H19" s="36" t="inlineStr">
+        <is>
+          <t>AUD 50 million</t>
+        </is>
+      </c>
+      <c r="I19" s="37" t="n">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="23" t="n">
+        <v>15</v>
+      </c>
+      <c r="B20" s="16" t="inlineStr">
+        <is>
+          <t>Arthur Andersen</t>
+        </is>
+      </c>
+      <c r="C20" s="16" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="D20" s="23" t="n">
+        <v>2002</v>
+      </c>
+      <c r="E20" s="16" t="inlineStr">
+        <is>
+          <t>Involvement in Enron Scandal and Failure in Ethical Responsibility</t>
+        </is>
+      </c>
+      <c r="F20" s="16" t="inlineStr">
+        <is>
+          <t>Conduct Risk</t>
+        </is>
+      </c>
+      <c r="G20" s="16" t="inlineStr">
+        <is>
+          <t>Compliance</t>
+        </is>
+      </c>
+      <c r="H20" s="16" t="inlineStr">
+        <is>
+          <t>$63 billion</t>
+        </is>
+      </c>
+      <c r="I20" s="34" t="n">
+        <v>63000</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="35" t="n">
+        <v>16</v>
+      </c>
+      <c r="B21" s="36" t="inlineStr">
+        <is>
+          <t>Banca Carige (Italy)</t>
+        </is>
+      </c>
+      <c r="C21" s="36" t="inlineStr">
+        <is>
+          <t>Italy</t>
+        </is>
+      </c>
+      <c r="D21" s="35" t="n">
+        <v>2018</v>
+      </c>
+      <c r="E21" s="36" t="inlineStr">
+        <is>
+          <t>Governance Failures and High NPLs</t>
+        </is>
+      </c>
+      <c r="F21" s="36" t="inlineStr">
+        <is>
+          <t>Credit Risk</t>
+        </is>
+      </c>
+      <c r="G21" s="36" t="inlineStr">
+        <is>
+          <t>Operations</t>
+        </is>
+      </c>
+      <c r="H21" s="36" t="inlineStr">
+        <is>
+          <t>€1.9 billion</t>
+        </is>
+      </c>
+      <c r="I21" s="37" t="n">
+        <v>2200</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="23" t="n">
+        <v>17</v>
+      </c>
+      <c r="B22" s="16" t="inlineStr">
+        <is>
+          <t>Banca Monte dei Paschi di Siena (Italy)</t>
+        </is>
+      </c>
+      <c r="C22" s="16" t="inlineStr">
+        <is>
+          <t>Italy</t>
+        </is>
+      </c>
+      <c r="D22" s="23" t="n">
+        <v>2013</v>
+      </c>
+      <c r="E22" s="16" t="inlineStr">
+        <is>
+          <t>Derivative and Accounting Fraud</t>
+        </is>
+      </c>
+      <c r="F22" s="16" t="inlineStr">
+        <is>
+          <t>Operational Risk</t>
+        </is>
+      </c>
+      <c r="G22" s="16" t="inlineStr">
+        <is>
+          <t>Reporting</t>
+        </is>
+      </c>
+      <c r="H22" s="16" t="inlineStr">
+        <is>
+          <t>€4 billion</t>
+        </is>
+      </c>
+      <c r="I22" s="34" t="n">
+        <v>4700</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="35" t="n">
+        <v>18</v>
+      </c>
+      <c r="B23" s="36" t="inlineStr">
+        <is>
+          <t>Banca Monte dei Paschi di Siena (Italy)</t>
+        </is>
+      </c>
+      <c r="C23" s="36" t="inlineStr">
+        <is>
+          <t>Italy</t>
+        </is>
+      </c>
+      <c r="D23" s="35" t="n">
+        <v>2013</v>
+      </c>
+      <c r="E23" s="36" t="inlineStr">
+        <is>
+          <t>Derivative Mis-selling</t>
+        </is>
+      </c>
+      <c r="F23" s="36" t="inlineStr">
+        <is>
+          <t>Conduct Risk</t>
+        </is>
+      </c>
+      <c r="G23" s="36" t="inlineStr">
+        <is>
+          <t>Compliance</t>
+        </is>
+      </c>
+      <c r="H23" s="36" t="inlineStr">
+        <is>
+          <t>€730 million</t>
+        </is>
+      </c>
+      <c r="I23" s="37" t="n">
+        <v>861</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="23" t="n">
+        <v>19</v>
+      </c>
+      <c r="B24" s="16" t="inlineStr">
+        <is>
+          <t>Banca Popolare di Bari (Italy)</t>
+        </is>
+      </c>
+      <c r="C24" s="16" t="inlineStr">
+        <is>
+          <t>Italy</t>
+        </is>
+      </c>
+      <c r="D24" s="23" t="n">
+        <v>2019</v>
+      </c>
+      <c r="E24" s="16" t="inlineStr">
+        <is>
+          <t>Mismanagement and False Accounting</t>
+        </is>
+      </c>
+      <c r="F24" s="16" t="inlineStr">
+        <is>
+          <t>Operational Risk</t>
+        </is>
+      </c>
+      <c r="G24" s="16" t="inlineStr">
+        <is>
+          <t>Reporting</t>
+        </is>
+      </c>
+      <c r="H24" s="16" t="inlineStr">
+        <is>
+          <t>€1.4 billion</t>
+        </is>
+      </c>
+      <c r="I24" s="34" t="n">
+        <v>1700</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="35" t="n">
+        <v>20</v>
+      </c>
+      <c r="B25" s="36" t="inlineStr">
+        <is>
+          <t>Banca Popolare di Vicenza (Italy)</t>
+        </is>
+      </c>
+      <c r="C25" s="36" t="inlineStr">
+        <is>
+          <t>Italy</t>
+        </is>
+      </c>
+      <c r="D25" s="35" t="n">
+        <v>2017</v>
+      </c>
+      <c r="E25" s="36" t="inlineStr">
+        <is>
+          <t>Fraud and Mismanagement</t>
+        </is>
+      </c>
+      <c r="F25" s="36" t="inlineStr">
+        <is>
+          <t>Operational Risk</t>
+        </is>
+      </c>
+      <c r="G25" s="36" t="inlineStr">
+        <is>
+          <t>Reporting</t>
+        </is>
+      </c>
+      <c r="H25" s="36" t="inlineStr">
+        <is>
+          <t>€11 billion</t>
+        </is>
+      </c>
+      <c r="I25" s="37" t="n">
+        <v>13000</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="23" t="n">
+        <v>21</v>
+      </c>
+      <c r="B26" s="16" t="inlineStr">
+        <is>
+          <t>Banca Privada d'Andorra (Andorra)</t>
+        </is>
+      </c>
+      <c r="C26" s="16" t="inlineStr">
+        <is>
+          <t>Andorra</t>
+        </is>
+      </c>
+      <c r="D26" s="23" t="n">
+        <v>2015</v>
+      </c>
+      <c r="E26" s="16" t="inlineStr">
+        <is>
+          <t>Money Laundering</t>
+        </is>
+      </c>
+      <c r="F26" s="16" t="inlineStr">
+        <is>
+          <t>Operational Risk</t>
+        </is>
+      </c>
+      <c r="G26" s="16" t="inlineStr">
+        <is>
+          <t>Compliance</t>
+        </is>
+      </c>
+      <c r="H26" s="16" t="inlineStr">
+        <is>
+          <t>$1.2 billion</t>
+        </is>
+      </c>
+      <c r="I26" s="34" t="n">
+        <v>1200</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="35" t="n">
+        <v>22</v>
+      </c>
+      <c r="B27" s="36" t="inlineStr">
+        <is>
+          <t>Banco de Valencia (Spain)</t>
+        </is>
+      </c>
+      <c r="C27" s="36" t="inlineStr">
+        <is>
+          <t>Spain</t>
+        </is>
+      </c>
+      <c r="D27" s="35" t="n">
+        <v>2011</v>
+      </c>
+      <c r="E27" s="36" t="inlineStr">
+        <is>
+          <t>Overexposure to Real Estate Loans</t>
+        </is>
+      </c>
+      <c r="F27" s="36" t="inlineStr">
+        <is>
+          <t>Credit Risk</t>
+        </is>
+      </c>
+      <c r="G27" s="36" t="inlineStr">
+        <is>
+          <t>Strategic</t>
+        </is>
+      </c>
+      <c r="H27" s="36" t="inlineStr">
+        <is>
+          <t>€4.5 billion</t>
+        </is>
+      </c>
+      <c r="I27" s="37" t="n">
+        <v>5300</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="23" t="n">
+        <v>23</v>
+      </c>
+      <c r="B28" s="16" t="inlineStr">
+        <is>
+          <t>Banco do Brasil</t>
+        </is>
+      </c>
+      <c r="C28" s="16" t="inlineStr">
+        <is>
+          <t>Brazil</t>
+        </is>
+      </c>
+      <c r="D28" s="23" t="n">
+        <v>2010</v>
+      </c>
+      <c r="E28" s="16" t="inlineStr">
+        <is>
+          <t>Fraud and Overextension of Credit</t>
+        </is>
+      </c>
+      <c r="F28" s="16" t="inlineStr">
+        <is>
+          <t>Operational Risk</t>
+        </is>
+      </c>
+      <c r="G28" s="16" t="inlineStr">
+        <is>
+          <t>Operations</t>
+        </is>
+      </c>
+      <c r="H28" s="16" t="inlineStr">
+        <is>
+          <t>$1.2 billion</t>
+        </is>
+      </c>
+      <c r="I28" s="34" t="n">
+        <v>1200</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="35" t="n">
+        <v>24</v>
+      </c>
+      <c r="B29" s="36" t="inlineStr">
+        <is>
+          <t>Banco Espirito Santo (Portugal)</t>
+        </is>
+      </c>
+      <c r="C29" s="36" t="inlineStr">
+        <is>
+          <t>Portugal</t>
+        </is>
+      </c>
+      <c r="D29" s="35" t="n">
+        <v>2014</v>
+      </c>
+      <c r="E29" s="36" t="inlineStr">
+        <is>
+          <t>Accounting Irregularities and Overexposure to Angola's Oil Sector</t>
+        </is>
+      </c>
+      <c r="F29" s="36" t="inlineStr">
+        <is>
+          <t>Operational Risk</t>
+        </is>
+      </c>
+      <c r="G29" s="36" t="inlineStr">
+        <is>
+          <t>Reporting</t>
+        </is>
+      </c>
+      <c r="H29" s="36" t="inlineStr">
+        <is>
+          <t>€3.6 billion</t>
+        </is>
+      </c>
+      <c r="I29" s="37" t="n">
+        <v>4200</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="23" t="n">
+        <v>25</v>
+      </c>
+      <c r="B30" s="16" t="inlineStr">
+        <is>
+          <t>Banco Intercontinental (Dominican Republic)</t>
+        </is>
+      </c>
+      <c r="C30" s="16" t="inlineStr">
+        <is>
+          <t>Dominican Republic</t>
+        </is>
+      </c>
+      <c r="D30" s="23" t="n">
+        <v>2003</v>
+      </c>
+      <c r="E30" s="16" t="inlineStr">
+        <is>
+          <t>Fraud and Mismanagement</t>
+        </is>
+      </c>
+      <c r="F30" s="16" t="inlineStr">
+        <is>
+          <t>Operational Risk</t>
+        </is>
+      </c>
+      <c r="G30" s="16" t="inlineStr">
+        <is>
+          <t>Operations</t>
+        </is>
+      </c>
+      <c r="H30" s="16" t="inlineStr">
+        <is>
+          <t>$2.2 billion</t>
+        </is>
+      </c>
+      <c r="I30" s="34" t="n">
+        <v>2200</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="35" t="n">
+        <v>26</v>
+      </c>
+      <c r="B31" s="36" t="inlineStr">
+        <is>
+          <t>Banco Nacional (Costa Rica)</t>
+        </is>
+      </c>
+      <c r="C31" s="36" t="inlineStr">
+        <is>
+          <t>Costa Rica</t>
+        </is>
+      </c>
+      <c r="D31" s="35" t="n">
+        <v>2004</v>
+      </c>
+      <c r="E31" s="36" t="inlineStr">
+        <is>
+          <t>Fraud and Money Laundering</t>
+        </is>
+      </c>
+      <c r="F31" s="36" t="inlineStr">
+        <is>
+          <t>Operational Risk</t>
+        </is>
+      </c>
+      <c r="G31" s="36" t="inlineStr">
+        <is>
+          <t>Compliance</t>
+        </is>
+      </c>
+      <c r="H31" s="36" t="inlineStr">
+        <is>
+          <t>$500 million</t>
+        </is>
+      </c>
+      <c r="I31" s="37" t="n">
+        <v>500</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="23" t="n">
+        <v>27</v>
+      </c>
+      <c r="B32" s="16" t="inlineStr">
+        <is>
+          <t>Banco Popular (Spain)</t>
+        </is>
+      </c>
+      <c r="C32" s="16" t="inlineStr">
+        <is>
+          <t>Spain</t>
+        </is>
+      </c>
+      <c r="D32" s="23" t="n">
+        <v>2017</v>
+      </c>
+      <c r="E32" s="16" t="inlineStr">
+        <is>
+          <t>Overexposure to Real Estate Loans</t>
+        </is>
+      </c>
+      <c r="F32" s="16" t="inlineStr">
+        <is>
+          <t>Credit Risk</t>
+        </is>
+      </c>
+      <c r="G32" s="16" t="inlineStr">
+        <is>
+          <t>Strategic</t>
+        </is>
+      </c>
+      <c r="H32" s="16" t="inlineStr">
+        <is>
+          <t>€3.5 billion</t>
+        </is>
+      </c>
+      <c r="I32" s="34" t="n">
+        <v>4100</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="35" t="n">
+        <v>28</v>
+      </c>
+      <c r="B33" s="36" t="inlineStr">
+        <is>
+          <t>Banesto (Spain)</t>
+        </is>
+      </c>
+      <c r="C33" s="36" t="inlineStr">
+        <is>
+          <t>Spain</t>
+        </is>
+      </c>
+      <c r="D33" s="35" t="n">
+        <v>1993</v>
+      </c>
+      <c r="E33" s="36" t="inlineStr">
+        <is>
+          <t>Overexposure to Real Estate Investments</t>
+        </is>
+      </c>
+      <c r="F33" s="36" t="inlineStr">
+        <is>
+          <t>Credit Risk</t>
+        </is>
+      </c>
+      <c r="G33" s="36" t="inlineStr">
+        <is>
+          <t>Strategic</t>
+        </is>
+      </c>
+      <c r="H33" s="36" t="inlineStr">
+        <is>
+          <t>$3.8 billion</t>
+        </is>
+      </c>
+      <c r="I33" s="37" t="n">
+        <v>3800</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="23" t="n">
+        <v>29</v>
+      </c>
+      <c r="B34" s="16" t="inlineStr">
+        <is>
+          <t>Bank of America</t>
+        </is>
+      </c>
+      <c r="C34" s="16" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="D34" s="23" t="n">
+        <v>2008</v>
+      </c>
+      <c r="E34" s="16" t="inlineStr">
+        <is>
+          <t>Overexposure to Subprime Mortgages</t>
+        </is>
+      </c>
+      <c r="F34" s="16" t="inlineStr">
+        <is>
+          <t>Credit Risk</t>
+        </is>
+      </c>
+      <c r="G34" s="16" t="inlineStr">
+        <is>
+          <t>Strategic</t>
+        </is>
+      </c>
+      <c r="H34" s="16" t="inlineStr">
+        <is>
+          <t>$64.8 billion</t>
+        </is>
+      </c>
+      <c r="I34" s="34" t="n">
+        <v>64800</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="35" t="n">
+        <v>30</v>
+      </c>
+      <c r="B35" s="36" t="inlineStr">
+        <is>
+          <t>Bank of Cyprus</t>
+        </is>
+      </c>
+      <c r="C35" s="36" t="inlineStr">
+        <is>
+          <t>Cyprus</t>
+        </is>
+      </c>
+      <c r="D35" s="35" t="n">
+        <v>2012</v>
+      </c>
+      <c r="E35" s="36" t="inlineStr">
+        <is>
+          <t>Overexposure to Greek Debt</t>
+        </is>
+      </c>
+      <c r="F35" s="36" t="inlineStr">
+        <is>
+          <t>Credit Risk</t>
+        </is>
+      </c>
+      <c r="G35" s="36" t="inlineStr">
+        <is>
+          <t>Strategic</t>
+        </is>
+      </c>
+      <c r="H35" s="36" t="inlineStr">
+        <is>
+          <t>€1.9 billion</t>
+        </is>
+      </c>
+      <c r="I35" s="37" t="n">
+        <v>2200</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="23" t="n">
+        <v>31</v>
+      </c>
+      <c r="B36" s="16" t="inlineStr">
+        <is>
+          <t>Bank of Moscow (Russia)</t>
+        </is>
+      </c>
+      <c r="C36" s="16" t="inlineStr">
+        <is>
+          <t>Russia</t>
+        </is>
+      </c>
+      <c r="D36" s="23" t="n">
+        <v>2011</v>
+      </c>
+      <c r="E36" s="16" t="inlineStr">
+        <is>
+          <t>Fraud and Mismanagement</t>
+        </is>
+      </c>
+      <c r="F36" s="16" t="inlineStr">
+        <is>
+          <t>Operational Risk</t>
+        </is>
+      </c>
+      <c r="G36" s="16" t="inlineStr">
+        <is>
+          <t>Operations</t>
+        </is>
+      </c>
+      <c r="H36" s="16" t="inlineStr">
+        <is>
+          <t>$9 billion</t>
+        </is>
+      </c>
+      <c r="I36" s="34" t="n">
+        <v>9000</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="35" t="n">
+        <v>32</v>
+      </c>
+      <c r="B37" s="36" t="inlineStr">
+        <is>
+          <t>Bank of New England</t>
+        </is>
+      </c>
+      <c r="C37" s="36" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="D37" s="35" t="n">
+        <v>1991</v>
+      </c>
+      <c r="E37" s="36" t="inlineStr">
+        <is>
+          <t>Overexposure to Commercial Real Estate</t>
+        </is>
+      </c>
+      <c r="F37" s="36" t="inlineStr">
+        <is>
+          <t>Credit Risk</t>
+        </is>
+      </c>
+      <c r="G37" s="36" t="inlineStr">
+        <is>
+          <t>Strategic</t>
+        </is>
+      </c>
+      <c r="H37" s="36" t="inlineStr">
+        <is>
+          <t>$2.5 billion</t>
+        </is>
+      </c>
+      <c r="I37" s="37" t="n">
+        <v>2500</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="23" t="n">
+        <v>33</v>
+      </c>
+      <c r="B38" s="16" t="inlineStr">
+        <is>
+          <t>Bankgesellschaft Berlin (Germany)</t>
+        </is>
+      </c>
+      <c r="C38" s="16" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="D38" s="23" t="n">
+        <v>2001</v>
+      </c>
+      <c r="E38" s="16" t="inlineStr">
+        <is>
+          <t>Overexposure to Real Estate Market</t>
+        </is>
+      </c>
+      <c r="F38" s="16" t="inlineStr">
+        <is>
+          <t>Credit Risk</t>
+        </is>
+      </c>
+      <c r="G38" s="16" t="inlineStr">
+        <is>
+          <t>Strategic</t>
+        </is>
+      </c>
+      <c r="H38" s="16" t="inlineStr">
+        <is>
+          <t>€1.6 billion</t>
+        </is>
+      </c>
+      <c r="I38" s="34" t="n">
+        <v>1900</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="35" t="n">
+        <v>34</v>
+      </c>
+      <c r="B39" s="36" t="inlineStr">
+        <is>
+          <t>Bankia (Spain)</t>
+        </is>
+      </c>
+      <c r="C39" s="36" t="inlineStr">
+        <is>
+          <t>Spain</t>
+        </is>
+      </c>
+      <c r="D39" s="35" t="n">
+        <v>2012</v>
+      </c>
+      <c r="E39" s="36" t="inlineStr">
+        <is>
+          <t>Overexposure to Real Estate Loans</t>
+        </is>
+      </c>
+      <c r="F39" s="36" t="inlineStr">
+        <is>
+          <t>Credit Risk</t>
+        </is>
+      </c>
+      <c r="G39" s="36" t="inlineStr">
+        <is>
+          <t>Strategic</t>
+        </is>
+      </c>
+      <c r="H39" s="36" t="inlineStr">
+        <is>
+          <t>€22.4 billion</t>
+        </is>
+      </c>
+      <c r="I39" s="37" t="n">
+        <v>26400</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="23" t="n">
+        <v>35</v>
+      </c>
+      <c r="B40" s="16" t="inlineStr">
+        <is>
+          <t>Bankia (Spain)</t>
+        </is>
+      </c>
+      <c r="C40" s="16" t="inlineStr">
+        <is>
+          <t>Spain</t>
+        </is>
+      </c>
+      <c r="D40" s="23" t="n">
+        <v>2012</v>
+      </c>
+      <c r="E40" s="16" t="inlineStr">
+        <is>
+          <t>Misrepresentation of Financial Statements</t>
+        </is>
+      </c>
+      <c r="F40" s="16" t="inlineStr">
+        <is>
+          <t>Operational Risk</t>
+        </is>
+      </c>
+      <c r="G40" s="16" t="inlineStr">
+        <is>
+          <t>Reporting</t>
+        </is>
+      </c>
+      <c r="H40" s="16" t="inlineStr">
+        <is>
+          <t>€3.1 billion</t>
+        </is>
+      </c>
+      <c r="I40" s="34" t="n">
+        <v>3700</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="35" t="n">
+        <v>36</v>
+      </c>
+      <c r="B41" s="36" t="inlineStr">
+        <is>
+          <t>BankUnited FSB</t>
+        </is>
+      </c>
+      <c r="C41" s="36" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="D41" s="35" t="n">
+        <v>2009</v>
+      </c>
+      <c r="E41" s="36" t="inlineStr">
+        <is>
+          <t>Overexposure to Option Adjustable-Rate Mortgages</t>
+        </is>
+      </c>
+      <c r="F41" s="36" t="inlineStr">
+        <is>
+          <t>Credit Risk</t>
+        </is>
+      </c>
+      <c r="G41" s="36" t="inlineStr">
+        <is>
+          <t>Strategic</t>
+        </is>
+      </c>
+      <c r="H41" s="36" t="inlineStr">
+        <is>
+          <t>$14 billion</t>
+        </is>
+      </c>
+      <c r="I41" s="37" t="n">
+        <v>14000</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="23" t="n">
+        <v>37</v>
+      </c>
+      <c r="B42" s="16" t="inlineStr">
+        <is>
+          <t>Barclays (UK)</t>
+        </is>
+      </c>
+      <c r="C42" s="16" t="inlineStr">
+        <is>
+          <t>United Kingdom</t>
+        </is>
+      </c>
+      <c r="D42" s="23" t="n">
+        <v>2012</v>
+      </c>
+      <c r="E42" s="16" t="inlineStr">
+        <is>
+          <t>Libor Scandal</t>
+        </is>
+      </c>
+      <c r="F42" s="16" t="inlineStr">
+        <is>
+          <t>Conduct Risk</t>
+        </is>
+      </c>
+      <c r="G42" s="16" t="inlineStr">
+        <is>
+          <t>Compliance</t>
+        </is>
+      </c>
+      <c r="H42" s="16" t="inlineStr">
+        <is>
+          <t>£290 million</t>
+        </is>
+      </c>
+      <c r="I42" s="34" t="n">
+        <v>392</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="35" t="n">
+        <v>38</v>
+      </c>
+      <c r="B43" s="36" t="inlineStr">
+        <is>
+          <t>Barings Bank</t>
+        </is>
+      </c>
+      <c r="C43" s="36" t="inlineStr">
+        <is>
+          <t>United Kingdom</t>
+        </is>
+      </c>
+      <c r="D43" s="35" t="n">
+        <v>1995</v>
+      </c>
+      <c r="E43" s="36" t="inlineStr">
+        <is>
+          <t>Unauthorized and Unsuitable Trading</t>
+        </is>
+      </c>
+      <c r="F43" s="36" t="inlineStr">
+        <is>
+          <t>Market Risk</t>
+        </is>
+      </c>
+      <c r="G43" s="36" t="inlineStr">
+        <is>
+          <t>Operations</t>
+        </is>
+      </c>
+      <c r="H43" s="36" t="inlineStr">
+        <is>
+          <t>$1.3 billion</t>
+        </is>
+      </c>
+      <c r="I43" s="37" t="n">
+        <v>1300</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="23" t="n">
+        <v>39</v>
+      </c>
+      <c r="B44" s="16" t="inlineStr">
+        <is>
+          <t>Bawag (Austria)</t>
+        </is>
+      </c>
+      <c r="C44" s="16" t="inlineStr">
+        <is>
+          <t>Austria</t>
+        </is>
+      </c>
+      <c r="D44" s="23" t="n">
+        <v>2006</v>
+      </c>
+      <c r="E44" s="16" t="inlineStr">
+        <is>
+          <t>Hidden Losses and Fraudulent Transactions</t>
+        </is>
+      </c>
+      <c r="F44" s="16" t="inlineStr">
+        <is>
+          <t>Operational Risk</t>
+        </is>
+      </c>
+      <c r="G44" s="16" t="inlineStr">
+        <is>
+          <t>Reporting</t>
+        </is>
+      </c>
+      <c r="H44" s="16" t="inlineStr">
+        <is>
+          <t>€1.6 billion</t>
+        </is>
+      </c>
+      <c r="I44" s="34" t="n">
+        <v>1900</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="35" t="n">
+        <v>40</v>
+      </c>
+      <c r="B45" s="36" t="inlineStr">
+        <is>
+          <t>Bear Stearns</t>
+        </is>
+      </c>
+      <c r="C45" s="36" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="D45" s="35" t="n">
+        <v>2008</v>
+      </c>
+      <c r="E45" s="36" t="inlineStr">
+        <is>
+          <t>Overexposure to Mortgage-Backed Securities</t>
+        </is>
+      </c>
+      <c r="F45" s="36" t="inlineStr">
+        <is>
+          <t>Credit Risk</t>
+        </is>
+      </c>
+      <c r="G45" s="36" t="inlineStr">
+        <is>
+          <t>Strategic</t>
+        </is>
+      </c>
+      <c r="H45" s="36" t="inlineStr">
+        <is>
+          <t>$17.3 billion</t>
+        </is>
+      </c>
+      <c r="I45" s="37" t="n">
+        <v>17300</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="23" t="n">
+        <v>41</v>
+      </c>
+      <c r="B46" s="16" t="inlineStr">
+        <is>
+          <t>Bear Stearns (US)</t>
+        </is>
+      </c>
+      <c r="C46" s="16" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="D46" s="23" t="n">
+        <v>2008</v>
+      </c>
+      <c r="E46" s="16" t="inlineStr">
+        <is>
+          <t>Overexposure to Collateralized Debt Obligations leading to insolvency</t>
+        </is>
+      </c>
+      <c r="F46" s="16" t="inlineStr">
+        <is>
+          <t>Credit Risk</t>
+        </is>
+      </c>
+      <c r="G46" s="16" t="inlineStr">
+        <is>
+          <t>Strategic</t>
+        </is>
+      </c>
+      <c r="H46" s="16" t="inlineStr">
+        <is>
+          <t>$3.2 billion</t>
+        </is>
+      </c>
+      <c r="I46" s="34" t="n">
+        <v>3200</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="35" t="n">
+        <v>42</v>
+      </c>
+      <c r="B47" s="36" t="inlineStr">
+        <is>
+          <t>Bernard L. Madoff Investment Securities LLC</t>
+        </is>
+      </c>
+      <c r="C47" s="36" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="D47" s="35" t="n">
+        <v>2008</v>
+      </c>
+      <c r="E47" s="36" t="inlineStr">
+        <is>
+          <t>Ponzi Scheme</t>
+        </is>
+      </c>
+      <c r="F47" s="36" t="inlineStr">
+        <is>
+          <t>Operational Risk</t>
+        </is>
+      </c>
+      <c r="G47" s="36" t="inlineStr">
+        <is>
+          <t>Compliance</t>
+        </is>
+      </c>
+      <c r="H47" s="36" t="inlineStr">
+        <is>
+          <t>$64.8 billion</t>
+        </is>
+      </c>
+      <c r="I47" s="37" t="n">
+        <v>64800</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="23" t="n">
+        <v>43</v>
+      </c>
+      <c r="B48" s="16" t="inlineStr">
+        <is>
+          <t>Bradford &amp; Bingley (UK)</t>
+        </is>
+      </c>
+      <c r="C48" s="16" t="inlineStr">
+        <is>
+          <t>United Kingdom</t>
+        </is>
+      </c>
+      <c r="D48" s="23" t="n">
+        <v>2008</v>
+      </c>
+      <c r="E48" s="16" t="inlineStr">
+        <is>
+          <t>Overexposure to Buy-to-Let Mortgages</t>
+        </is>
+      </c>
+      <c r="F48" s="16" t="inlineStr">
+        <is>
+          <t>Credit Risk</t>
+        </is>
+      </c>
+      <c r="G48" s="16" t="inlineStr">
+        <is>
+          <t>Strategic</t>
+        </is>
+      </c>
+      <c r="H48" s="16" t="inlineStr">
+        <is>
+          <t>£11 billion</t>
+        </is>
+      </c>
+      <c r="I48" s="34" t="n">
+        <v>14900</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="35" t="n">
+        <v>44</v>
+      </c>
+      <c r="B49" s="36" t="inlineStr">
+        <is>
+          <t>Bradford &amp; Bingley (UK)</t>
+        </is>
+      </c>
+      <c r="C49" s="36" t="inlineStr">
+        <is>
+          <t>United Kingdom</t>
+        </is>
+      </c>
+      <c r="D49" s="35" t="n">
+        <v>2008</v>
+      </c>
+      <c r="E49" s="36" t="inlineStr">
+        <is>
+          <t>Overexposure to Subprime Mortgages</t>
+        </is>
+      </c>
+      <c r="F49" s="36" t="inlineStr">
+        <is>
+          <t>Credit Risk</t>
+        </is>
+      </c>
+      <c r="G49" s="36" t="inlineStr">
+        <is>
+          <t>Operations</t>
+        </is>
+      </c>
+      <c r="H49" s="36" t="inlineStr">
+        <is>
+          <t>£18 billion</t>
+        </is>
+      </c>
+      <c r="I49" s="37" t="n">
+        <v>24300</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="23" t="n">
+        <v>45</v>
+      </c>
+      <c r="B50" s="16" t="inlineStr">
+        <is>
+          <t>Bradford &amp; Bingley (UK)</t>
+        </is>
+      </c>
+      <c r="C50" s="16" t="inlineStr">
+        <is>
+          <t>United Kingdom</t>
+        </is>
+      </c>
+      <c r="D50" s="23" t="n">
+        <v>2008</v>
+      </c>
+      <c r="E50" s="16" t="inlineStr">
+        <is>
+          <t>Overexposure to Mortgage Market leading to insolvency</t>
+        </is>
+      </c>
+      <c r="F50" s="16" t="inlineStr">
+        <is>
+          <t>Credit Risk</t>
+        </is>
+      </c>
+      <c r="G50" s="16" t="inlineStr">
+        <is>
+          <t>Strategic</t>
+        </is>
+      </c>
+      <c r="H50" s="16" t="inlineStr">
+        <is>
+          <t>£11 billion</t>
+        </is>
+      </c>
+      <c r="I50" s="34" t="n">
+        <v>14900</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="35" t="n">
+        <v>46</v>
+      </c>
+      <c r="B51" s="36" t="inlineStr">
+        <is>
+          <t>Caisse Centrale du Credit Immobilier de France (3CIF)</t>
+        </is>
+      </c>
+      <c r="C51" s="36" t="inlineStr">
+        <is>
+          <t>France</t>
+        </is>
+      </c>
+      <c r="D51" s="35" t="n">
+        <v>2012</v>
+      </c>
+      <c r="E51" s="36" t="inlineStr">
+        <is>
+          <t>Overexposure to Real Estate Market</t>
+        </is>
+      </c>
+      <c r="F51" s="36" t="inlineStr">
+        <is>
+          <t>Credit Risk</t>
+        </is>
+      </c>
+      <c r="G51" s="36" t="inlineStr">
+        <is>
+          <t>Strategic</t>
+        </is>
+      </c>
+      <c r="H51" s="36" t="inlineStr">
+        <is>
+          <t>€1.7 billion</t>
+        </is>
+      </c>
+      <c r="I51" s="37" t="n">
+        <v>2000</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="23" t="n">
+        <v>47</v>
+      </c>
+      <c r="B52" s="16" t="inlineStr">
+        <is>
+          <t>Caixa Economica Federal (Brazil)</t>
+        </is>
+      </c>
+      <c r="C52" s="16" t="inlineStr">
+        <is>
+          <t>Brazil</t>
+        </is>
+      </c>
+      <c r="D52" s="23" t="n">
+        <v>2015</v>
+      </c>
+      <c r="E52" s="16" t="inlineStr">
+        <is>
+          <t>Corruption and Fraud</t>
+        </is>
+      </c>
+      <c r="F52" s="16" t="inlineStr">
+        <is>
+          <t>Operational Risk</t>
+        </is>
+      </c>
+      <c r="G52" s="16" t="inlineStr">
+        <is>
+          <t>Compliance</t>
+        </is>
+      </c>
+      <c r="H52" s="16" t="inlineStr">
+        <is>
+          <t>$2 billion</t>
+        </is>
+      </c>
+      <c r="I52" s="34" t="n">
+        <v>2000</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="35" t="n">
+        <v>48</v>
+      </c>
+      <c r="B53" s="36" t="inlineStr">
+        <is>
+          <t>Caixa Geral de Depositos (Portugal)</t>
+        </is>
+      </c>
+      <c r="C53" s="36" t="inlineStr">
+        <is>
+          <t>Portugal</t>
+        </is>
+      </c>
+      <c r="D53" s="35" t="n">
+        <v>2016</v>
+      </c>
+      <c r="E53" s="36" t="inlineStr">
+        <is>
+          <t>Mismanagement and Risky Business Practice</t>
+        </is>
+      </c>
+      <c r="F53" s="36" t="inlineStr">
+        <is>
+          <t>Operational Risk</t>
+        </is>
+      </c>
+      <c r="G53" s="36" t="inlineStr">
+        <is>
+          <t>Operations</t>
+        </is>
+      </c>
+      <c r="H53" s="36" t="inlineStr">
+        <is>
+          <t>€1.86 billion</t>
+        </is>
+      </c>
+      <c r="I53" s="37" t="n">
+        <v>2200</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="23" t="n">
+        <v>49</v>
+      </c>
+      <c r="B54" s="16" t="inlineStr">
+        <is>
+          <t>Caja Madrid (Spain)</t>
+        </is>
+      </c>
+      <c r="C54" s="16" t="inlineStr">
+        <is>
+          <t>Spain</t>
+        </is>
+      </c>
+      <c r="D54" s="23" t="n">
+        <v>2013</v>
+      </c>
+      <c r="E54" s="16" t="inlineStr">
+        <is>
+          <t>Credit Card Scandal and Mismanagement</t>
+        </is>
+      </c>
+      <c r="F54" s="16" t="inlineStr">
+        <is>
+          <t>Credit Risk</t>
+        </is>
+      </c>
+      <c r="G54" s="16" t="inlineStr">
+        <is>
+          <t>Operations</t>
+        </is>
+      </c>
+      <c r="H54" s="16" t="inlineStr">
+        <is>
+          <t>€15 billion</t>
+        </is>
+      </c>
+      <c r="I54" s="34" t="n">
+        <v>17700</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="35" t="n">
+        <v>50</v>
+      </c>
+      <c r="B55" s="36" t="inlineStr">
+        <is>
+          <t>Capital One (US)</t>
+        </is>
+      </c>
+      <c r="C55" s="36" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="D55" s="35" t="n">
+        <v>2019</v>
+      </c>
+      <c r="E55" s="36" t="inlineStr">
+        <is>
+          <t>Data Breach exposing customer data</t>
+        </is>
+      </c>
+      <c r="F55" s="36" t="inlineStr">
+        <is>
+          <t>Operational Risk</t>
+        </is>
+      </c>
+      <c r="G55" s="36" t="inlineStr">
+        <is>
+          <t>Operations</t>
+        </is>
+      </c>
+      <c r="H55" s="36" t="inlineStr">
+        <is>
+          <t>$300 million</t>
+        </is>
+      </c>
+      <c r="I55" s="37" t="n">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="23" t="n">
+        <v>51</v>
+      </c>
+      <c r="B56" s="16" t="inlineStr">
+        <is>
+          <t>Carige Bank (Italy)</t>
+        </is>
+      </c>
+      <c r="C56" s="16" t="inlineStr">
+        <is>
+          <t>Italy</t>
+        </is>
+      </c>
+      <c r="D56" s="23" t="n">
+        <v>2018</v>
+      </c>
+      <c r="E56" s="16" t="inlineStr">
+        <is>
+          <t>Poor Governance and Risk Management</t>
+        </is>
+      </c>
+      <c r="F56" s="16" t="inlineStr">
+        <is>
+          <t>Operational Risk</t>
+        </is>
+      </c>
+      <c r="G56" s="16" t="inlineStr">
+        <is>
+          <t>Operations</t>
+        </is>
+      </c>
+      <c r="H56" s="16" t="inlineStr">
+        <is>
+          <t>€500 million</t>
+        </is>
+      </c>
+      <c r="I56" s="34" t="n">
+        <v>590</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="35" t="n">
+        <v>52</v>
+      </c>
+      <c r="B57" s="36" t="inlineStr">
+        <is>
+          <t>Carillion (UK)</t>
+        </is>
+      </c>
+      <c r="C57" s="36" t="inlineStr">
+        <is>
+          <t>United Kingdom</t>
+        </is>
+      </c>
+      <c r="D57" s="35" t="n">
+        <v>2018</v>
+      </c>
+      <c r="E57" s="36" t="inlineStr">
+        <is>
+          <t>Debt and Pension Deficit Mismanagement</t>
+        </is>
+      </c>
+      <c r="F57" s="36" t="inlineStr">
+        <is>
+          <t>Credit Risk</t>
+        </is>
+      </c>
+      <c r="G57" s="36" t="inlineStr">
+        <is>
+          <t>Strategic</t>
+        </is>
+      </c>
+      <c r="H57" s="36" t="inlineStr">
+        <is>
+          <t>£1.5 billion</t>
+        </is>
+      </c>
+      <c r="I57" s="37" t="n">
+        <v>2000</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="23" t="n">
+        <v>53</v>
+      </c>
+      <c r="B58" s="16" t="inlineStr">
+        <is>
+          <t>CIT Group</t>
+        </is>
+      </c>
+      <c r="C58" s="16" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="D58" s="23" t="n">
+        <v>2009</v>
+      </c>
+      <c r="E58" s="16" t="inlineStr">
+        <is>
+          <t>Overexposure to Subprime Mortgages</t>
+        </is>
+      </c>
+      <c r="F58" s="16" t="inlineStr">
+        <is>
+          <t>Credit Risk</t>
+        </is>
+      </c>
+      <c r="G58" s="16" t="inlineStr">
+        <is>
+          <t>Strategic</t>
+        </is>
+      </c>
+      <c r="H58" s="16" t="inlineStr">
+        <is>
+          <t>$2.3 billion</t>
+        </is>
+      </c>
+      <c r="I58" s="34" t="n">
+        <v>2300</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="35" t="n">
+        <v>54</v>
+      </c>
+      <c r="B59" s="36" t="inlineStr">
+        <is>
+          <t>Citigroup</t>
+        </is>
+      </c>
+      <c r="C59" s="36" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="D59" s="35" t="n">
+        <v>2008</v>
+      </c>
+      <c r="E59" s="36" t="inlineStr">
+        <is>
+          <t>Overexposure to Subprime Mortgages</t>
+        </is>
+      </c>
+      <c r="F59" s="36" t="inlineStr">
+        <is>
+          <t>Credit Risk</t>
+        </is>
+      </c>
+      <c r="G59" s="36" t="inlineStr">
+        <is>
+          <t>Strategic</t>
+        </is>
+      </c>
+      <c r="H59" s="36" t="inlineStr">
+        <is>
+          <t>$27.7 billion</t>
+        </is>
+      </c>
+      <c r="I59" s="37" t="n">
+        <v>27700</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="23" t="n">
+        <v>55</v>
+      </c>
+      <c r="B60" s="16" t="inlineStr">
+        <is>
+          <t>Colonial BancGroup</t>
+        </is>
+      </c>
+      <c r="C60" s="16" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="D60" s="23" t="n">
+        <v>2009</v>
+      </c>
+      <c r="E60" s="16" t="inlineStr">
+        <is>
+          <t>Overexposure to Mortgage-backed Securities and Fraud</t>
+        </is>
+      </c>
+      <c r="F60" s="16" t="inlineStr">
+        <is>
+          <t>Operational Risk</t>
+        </is>
+      </c>
+      <c r="G60" s="16" t="inlineStr">
+        <is>
+          <t>Operations</t>
+        </is>
+      </c>
+      <c r="H60" s="16" t="inlineStr">
+        <is>
+          <t>$2.8 billion</t>
+        </is>
+      </c>
+      <c r="I60" s="34" t="n">
+        <v>2800</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="35" t="n">
+        <v>56</v>
+      </c>
+      <c r="B61" s="36" t="inlineStr">
+        <is>
+          <t>Commerzbank (Germany)</t>
+        </is>
+      </c>
+      <c r="C61" s="36" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="D61" s="35" t="n">
+        <v>2008</v>
+      </c>
+      <c r="E61" s="36" t="inlineStr">
+        <is>
+          <t>Overexposure to Subprime Mortgages</t>
+        </is>
+      </c>
+      <c r="F61" s="36" t="inlineStr">
+        <is>
+          <t>Credit Risk</t>
+        </is>
+      </c>
+      <c r="G61" s="36" t="inlineStr">
+        <is>
+          <t>Strategic</t>
+        </is>
+      </c>
+      <c r="H61" s="36" t="inlineStr">
+        <is>
+          <t>€6.5 billion</t>
+        </is>
+      </c>
+      <c r="I61" s="37" t="n">
+        <v>7700</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="23" t="n">
+        <v>57</v>
+      </c>
+      <c r="B62" s="16" t="inlineStr">
+        <is>
+          <t>Commonwealth Bank (Australia)</t>
+        </is>
+      </c>
+      <c r="C62" s="16" t="inlineStr">
+        <is>
+          <t>Australia</t>
+        </is>
+      </c>
+      <c r="D62" s="23" t="n">
+        <v>2018</v>
+      </c>
+      <c r="E62" s="16" t="inlineStr">
+        <is>
+          <t>Money Laundering</t>
+        </is>
+      </c>
+      <c r="F62" s="16" t="inlineStr">
+        <is>
+          <t>Operational Risk</t>
+        </is>
+      </c>
+      <c r="G62" s="16" t="inlineStr">
+        <is>
+          <t>Compliance</t>
+        </is>
+      </c>
+      <c r="H62" s="16" t="inlineStr">
+        <is>
+          <t>AUD 700 million</t>
+        </is>
+      </c>
+      <c r="I62" s="34" t="n">
+        <v>504</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="35" t="n">
+        <v>58</v>
+      </c>
+      <c r="B63" s="36" t="inlineStr">
+        <is>
+          <t>Cooperative Bank (UK)</t>
+        </is>
+      </c>
+      <c r="C63" s="36" t="inlineStr">
+        <is>
+          <t>United Kingdom</t>
+        </is>
+      </c>
+      <c r="D63" s="35" t="n">
+        <v>2013</v>
+      </c>
+      <c r="E63" s="36" t="inlineStr">
+        <is>
+          <t>Mismanagement and Governance Failures</t>
+        </is>
+      </c>
+      <c r="F63" s="36" t="inlineStr">
+        <is>
+          <t>Operational Risk</t>
+        </is>
+      </c>
+      <c r="G63" s="36" t="inlineStr">
+        <is>
+          <t>Operations</t>
+        </is>
+      </c>
+      <c r="H63" s="36" t="inlineStr">
+        <is>
+          <t>£1.5 billion</t>
+        </is>
+      </c>
+      <c r="I63" s="37" t="n">
+        <v>2000</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="23" t="n">
+        <v>59</v>
+      </c>
+      <c r="B64" s="16" t="inlineStr">
+        <is>
+          <t>Countrywide Financial</t>
+        </is>
+      </c>
+      <c r="C64" s="16" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="D64" s="23" t="n">
+        <v>2008</v>
+      </c>
+      <c r="E64" s="16" t="inlineStr">
+        <is>
+          <t>Subprime Mortgage Lending and Fraud</t>
+        </is>
+      </c>
+      <c r="F64" s="16" t="inlineStr">
+        <is>
+          <t>Operational Risk</t>
+        </is>
+      </c>
+      <c r="G64" s="16" t="inlineStr">
+        <is>
+          <t>Strategic</t>
+        </is>
+      </c>
+      <c r="H64" s="16" t="inlineStr">
+        <is>
+          <t>$8.7 billion</t>
+        </is>
+      </c>
+      <c r="I64" s="34" t="n">
+        <v>8700</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="35" t="n">
+        <v>60</v>
+      </c>
+      <c r="B65" s="36" t="inlineStr">
+        <is>
+          <t>Credit Suisse (Switzerland)</t>
+        </is>
+      </c>
+      <c r="C65" s="36" t="inlineStr">
+        <is>
+          <t>Switzerland</t>
+        </is>
+      </c>
+      <c r="D65" s="35" t="n">
+        <v>2008</v>
+      </c>
+      <c r="E65" s="36" t="inlineStr">
+        <is>
+          <t>Overexposure to Subprime Mortgages</t>
+        </is>
+      </c>
+      <c r="F65" s="36" t="inlineStr">
+        <is>
+          <t>Credit Risk</t>
+        </is>
+      </c>
+      <c r="G65" s="36" t="inlineStr">
+        <is>
+          <t>Strategic</t>
+        </is>
+      </c>
+      <c r="H65" s="36" t="inlineStr">
+        <is>
+          <t>$2.85 billion</t>
+        </is>
+      </c>
+      <c r="I65" s="37" t="n">
+        <v>2900</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="23" t="n">
+        <v>61</v>
+      </c>
+      <c r="B66" s="16" t="inlineStr">
+        <is>
+          <t>Credit Suisse (Switzerland)</t>
+        </is>
+      </c>
+      <c r="C66" s="16" t="inlineStr">
+        <is>
+          <t>Switzerland</t>
+        </is>
+      </c>
+      <c r="D66" s="23" t="n">
+        <v>2016</v>
+      </c>
+      <c r="E66" s="16" t="inlineStr">
+        <is>
+          <t>Mozambique's Hidden Debt Scandal</t>
+        </is>
+      </c>
+      <c r="F66" s="16" t="inlineStr">
+        <is>
+          <t>Credit Risk</t>
+        </is>
+      </c>
+      <c r="G66" s="16" t="inlineStr">
+        <is>
+          <t>Compliance</t>
+        </is>
+      </c>
+      <c r="H66" s="16" t="inlineStr">
+        <is>
+          <t>$2 billion</t>
+        </is>
+      </c>
+      <c r="I66" s="34" t="n">
+        <v>2000</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="35" t="n">
+        <v>62</v>
+      </c>
+      <c r="B67" s="36" t="inlineStr">
+        <is>
+          <t>Credit Suisse (Switzerland)</t>
+        </is>
+      </c>
+      <c r="C67" s="36" t="inlineStr">
+        <is>
+          <t>Switzerland</t>
+        </is>
+      </c>
+      <c r="D67" s="35" t="n">
+        <v>2020</v>
+      </c>
+      <c r="E67" s="36" t="inlineStr">
+        <is>
+          <t>Spying Scandal</t>
+        </is>
+      </c>
+      <c r="F67" s="36" t="inlineStr">
+        <is>
+          <t>Operational Risk</t>
+        </is>
+      </c>
+      <c r="G67" s="36" t="inlineStr">
+        <is>
+          <t>Operations</t>
+        </is>
+      </c>
+      <c r="H67" s="36" t="inlineStr">
+        <is>
+          <t>CHF 5 million</t>
+        </is>
+      </c>
+      <c r="I67" s="37" t="n">
+        <v>5.5</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="23" t="n">
+        <v>63</v>
+      </c>
+      <c r="B68" s="16" t="inlineStr">
+        <is>
+          <t>Danske Bank (Denmark)</t>
+        </is>
+      </c>
+      <c r="C68" s="16" t="inlineStr">
+        <is>
+          <t>Denmark</t>
+        </is>
+      </c>
+      <c r="D68" s="23" t="n">
+        <v>2018</v>
+      </c>
+      <c r="E68" s="16" t="inlineStr">
+        <is>
+          <t>Money Laundering (200 billion)</t>
+        </is>
+      </c>
+      <c r="F68" s="16" t="inlineStr">
+        <is>
+          <t>Operational Risk</t>
+        </is>
+      </c>
+      <c r="G68" s="16" t="inlineStr">
+        <is>
+          <t>Compliance</t>
+        </is>
+      </c>
+      <c r="H68" s="16" t="inlineStr">
+        <is>
+          <t>DKK 1.5 billion</t>
+        </is>
+      </c>
+      <c r="I68" s="34" t="n">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="35" t="n">
+        <v>64</v>
+      </c>
+      <c r="B69" s="36" t="inlineStr">
+        <is>
+          <t>DBS (Singapore)</t>
+        </is>
+      </c>
+      <c r="C69" s="36" t="inlineStr">
+        <is>
+          <t>Singapore</t>
+        </is>
+      </c>
+      <c r="D69" s="35" t="n">
+        <v>2008</v>
+      </c>
+      <c r="E69" s="36" t="inlineStr">
+        <is>
+          <t>Overexposure to Lehman Brothers' Structured Products</t>
+        </is>
+      </c>
+      <c r="F69" s="36" t="inlineStr">
+        <is>
+          <t>Credit Risk</t>
+        </is>
+      </c>
+      <c r="G69" s="36" t="inlineStr">
+        <is>
+          <t>Operations</t>
+        </is>
+      </c>
+      <c r="H69" s="36" t="inlineStr">
+        <is>
+          <t>SGD 1.03 billion</t>
+        </is>
+      </c>
+      <c r="I69" s="37" t="n">
+        <v>762</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="23" t="n">
+        <v>65</v>
+      </c>
+      <c r="B70" s="16" t="inlineStr">
+        <is>
+          <t>Delta National Bank and Trust Company (US)</t>
+        </is>
+      </c>
+      <c r="C70" s="16" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="D70" s="23" t="n">
+        <v>2008</v>
+      </c>
+      <c r="E70" s="16" t="inlineStr">
+        <is>
+          <t>Subprime Mortgage Crisis</t>
+        </is>
+      </c>
+      <c r="F70" s="16" t="inlineStr">
+        <is>
+          <t>Credit Risk</t>
+        </is>
+      </c>
+      <c r="G70" s="16" t="inlineStr">
+        <is>
+          <t>Strategic</t>
+        </is>
+      </c>
+      <c r="H70" s="16" t="inlineStr">
+        <is>
+          <t>$500 million</t>
+        </is>
+      </c>
+      <c r="I70" s="34" t="n">
+        <v>500</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="35" t="n">
+        <v>66</v>
+      </c>
+      <c r="B71" s="36" t="inlineStr">
+        <is>
+          <t>Depfa Bank (Germany)</t>
+        </is>
+      </c>
+      <c r="C71" s="36" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="D71" s="35" t="n">
+        <v>2008</v>
+      </c>
+      <c r="E71" s="36" t="inlineStr">
+        <is>
+          <t>Overexposure to Public Sector Funding during Financial Crisis</t>
+        </is>
+      </c>
+      <c r="F71" s="36" t="inlineStr">
+        <is>
+          <t>Credit Risk</t>
+        </is>
+      </c>
+      <c r="G71" s="36" t="inlineStr">
+        <is>
+          <t>Strategic</t>
+        </is>
+      </c>
+      <c r="H71" s="36" t="inlineStr">
+        <is>
+          <t>€2.6 billion</t>
+        </is>
+      </c>
+      <c r="I71" s="37" t="n">
+        <v>3100</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="23" t="n">
+        <v>67</v>
+      </c>
+      <c r="B72" s="16" t="inlineStr">
+        <is>
+          <t>Deutsche Bank (Germany)</t>
+        </is>
+      </c>
+      <c r="C72" s="16" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="D72" s="23" t="n">
+        <v>2018</v>
+      </c>
+      <c r="E72" s="16" t="inlineStr">
+        <is>
+          <t>Money Laundering</t>
+        </is>
+      </c>
+      <c r="F72" s="16" t="inlineStr">
+        <is>
+          <t>Operational Risk</t>
+        </is>
+      </c>
+      <c r="G72" s="16" t="inlineStr">
+        <is>
+          <t>Compliance</t>
+        </is>
+      </c>
+      <c r="H72" s="16" t="inlineStr">
+        <is>
+          <t>$630 million</t>
+        </is>
+      </c>
+      <c r="I72" s="34" t="n">
+        <v>630</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="35" t="n">
+        <v>68</v>
+      </c>
+      <c r="B73" s="36" t="inlineStr">
+        <is>
+          <t>Dewan Housing Finance Corporation (India)</t>
+        </is>
+      </c>
+      <c r="C73" s="36" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="D73" s="35" t="n">
+        <v>2019</v>
+      </c>
+      <c r="E73" s="36" t="inlineStr">
+        <is>
+          <t>Fraud and Mismanagement</t>
+        </is>
+      </c>
+      <c r="F73" s="36" t="inlineStr">
+        <is>
+          <t>Operational Risk</t>
+        </is>
+      </c>
+      <c r="G73" s="36" t="inlineStr">
+        <is>
+          <t>Operations</t>
+        </is>
+      </c>
+      <c r="H73" s="36" t="inlineStr">
+        <is>
+          <t>$4 billion</t>
+        </is>
+      </c>
+      <c r="I73" s="37" t="n">
+        <v>4000</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="23" t="n">
+        <v>69</v>
+      </c>
+      <c r="B74" s="16" t="inlineStr">
+        <is>
+          <t>Dexia (Belgium)</t>
+        </is>
+      </c>
+      <c r="C74" s="16" t="inlineStr">
+        <is>
+          <t>Belgium</t>
+        </is>
+      </c>
+      <c r="D74" s="23" t="n">
+        <v>2011</v>
+      </c>
+      <c r="E74" s="16" t="inlineStr">
+        <is>
+          <t>Overexposure to Greek Debt</t>
+        </is>
+      </c>
+      <c r="F74" s="16" t="inlineStr">
+        <is>
+          <t>Credit Risk</t>
+        </is>
+      </c>
+      <c r="G74" s="16" t="inlineStr">
+        <is>
+          <t>Strategic</t>
+        </is>
+      </c>
+      <c r="H74" s="16" t="inlineStr">
+        <is>
+          <t>€4 billion</t>
+        </is>
+      </c>
+      <c r="I74" s="34" t="n">
+        <v>4700</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="35" t="n">
+        <v>70</v>
+      </c>
+      <c r="B75" s="36" t="inlineStr">
+        <is>
+          <t>Enron</t>
+        </is>
+      </c>
+      <c r="C75" s="36" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="D75" s="35" t="n">
+        <v>2001</v>
+      </c>
+      <c r="E75" s="36" t="inlineStr">
+        <is>
+          <t>Accounting Fraud</t>
+        </is>
+      </c>
+      <c r="F75" s="36" t="inlineStr">
+        <is>
+          <t>Operational Risk</t>
+        </is>
+      </c>
+      <c r="G75" s="36" t="inlineStr">
+        <is>
+          <t>Reporting</t>
+        </is>
+      </c>
+      <c r="H75" s="36" t="inlineStr">
+        <is>
+          <t>$74 billion</t>
+        </is>
+      </c>
+      <c r="I75" s="37" t="n">
+        <v>74000</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="23" t="n">
+        <v>71</v>
+      </c>
+      <c r="B76" s="16" t="inlineStr">
+        <is>
+          <t>Equifax (US)</t>
+        </is>
+      </c>
+      <c r="C76" s="16" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="D76" s="23" t="n">
+        <v>2017</v>
+      </c>
+      <c r="E76" s="16" t="inlineStr">
+        <is>
+          <t>Data Breach</t>
+        </is>
+      </c>
+      <c r="F76" s="16" t="inlineStr">
+        <is>
+          <t>Operational Risk</t>
+        </is>
+      </c>
+      <c r="G76" s="16" t="inlineStr">
+        <is>
+          <t>Operations</t>
+        </is>
+      </c>
+      <c r="H76" s="16" t="inlineStr">
+        <is>
+          <t>$1.38 billion</t>
+        </is>
+      </c>
+      <c r="I76" s="34" t="n">
+        <v>1400</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" s="35" t="n">
+        <v>72</v>
+      </c>
+      <c r="B77" s="36" t="inlineStr">
+        <is>
+          <t>Equitable Life (UK)</t>
+        </is>
+      </c>
+      <c r="C77" s="36" t="inlineStr">
+        <is>
+          <t>United Kingdom</t>
+        </is>
+      </c>
+      <c r="D77" s="35" t="n">
+        <v>2000</v>
+      </c>
+      <c r="E77" s="36" t="inlineStr">
+        <is>
+          <t>Over-optimistic valuation of liabilities leading to insolvency</t>
+        </is>
+      </c>
+      <c r="F77" s="36" t="inlineStr">
+        <is>
+          <t>Liquidity Risk</t>
+        </is>
+      </c>
+      <c r="G77" s="36" t="inlineStr">
+        <is>
+          <t>Strategic</t>
+        </is>
+      </c>
+      <c r="H77" s="36" t="inlineStr">
+        <is>
+          <t>£1.5 billion</t>
+        </is>
+      </c>
+      <c r="I77" s="37" t="n">
+        <v>2000</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="23" t="n">
+        <v>73</v>
+      </c>
+      <c r="B78" s="16" t="inlineStr">
+        <is>
+          <t>Erste Group Bank (Austria)</t>
+        </is>
+      </c>
+      <c r="C78" s="16" t="inlineStr">
+        <is>
+          <t>Austria</t>
+        </is>
+      </c>
+      <c r="D78" s="23" t="n">
+        <v>2014</v>
+      </c>
+      <c r="E78" s="16" t="inlineStr">
+        <is>
+          <t>Overexposure to Eastern European Markets</t>
+        </is>
+      </c>
+      <c r="F78" s="16" t="inlineStr">
+        <is>
+          <t>Credit Risk</t>
+        </is>
+      </c>
+      <c r="G78" s="16" t="inlineStr">
+        <is>
+          <t>Strategic</t>
+        </is>
+      </c>
+      <c r="H78" s="16" t="inlineStr">
+        <is>
+          <t>€1.6 billion</t>
+        </is>
+      </c>
+      <c r="I78" s="34" t="n">
+        <v>1900</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" s="35" t="n">
+        <v>74</v>
+      </c>
+      <c r="B79" s="36" t="inlineStr">
+        <is>
+          <t>Fannie Mae</t>
+        </is>
+      </c>
+      <c r="C79" s="36" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="D79" s="35" t="n">
+        <v>2004</v>
+      </c>
+      <c r="E79" s="36" t="inlineStr">
+        <is>
+          <t>Accounting Fraud</t>
+        </is>
+      </c>
+      <c r="F79" s="36" t="inlineStr">
+        <is>
+          <t>Operational Risk</t>
+        </is>
+      </c>
+      <c r="G79" s="36" t="inlineStr">
+        <is>
+          <t>Reporting</t>
+        </is>
+      </c>
+      <c r="H79" s="36" t="inlineStr">
+        <is>
+          <t>$11 billion</t>
+        </is>
+      </c>
+      <c r="I79" s="37" t="n">
+        <v>11000</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="23" t="n">
+        <v>75</v>
+      </c>
+      <c r="B80" s="16" t="inlineStr">
+        <is>
+          <t>Fannie Mae and Freddie Mac</t>
+        </is>
+      </c>
+      <c r="C80" s="16" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="D80" s="23" t="n">
+        <v>2008</v>
+      </c>
+      <c r="E80" s="16" t="inlineStr">
+        <is>
+          <t>Overexposure to Mortgage-backed Securities</t>
+        </is>
+      </c>
+      <c r="F80" s="16" t="inlineStr">
+        <is>
+          <t>Credit Risk</t>
+        </is>
+      </c>
+      <c r="G80" s="16" t="inlineStr">
+        <is>
+          <t>Strategic</t>
+        </is>
+      </c>
+      <c r="H80" s="16" t="inlineStr">
+        <is>
+          <t>$187 billion</t>
+        </is>
+      </c>
+      <c r="I80" s="34" t="n">
+        <v>187000</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" s="35" t="n">
+        <v>76</v>
+      </c>
+      <c r="B81" s="36" t="inlineStr">
+        <is>
+          <t>First National Bank of Keystone (USA)</t>
+        </is>
+      </c>
+      <c r="C81" s="36" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="D81" s="35" t="n">
+        <v>1999</v>
+      </c>
+      <c r="E81" s="36" t="inlineStr">
+        <is>
+          <t>Fraud and Operational Risk</t>
+        </is>
+      </c>
+      <c r="F81" s="36" t="inlineStr">
+        <is>
+          <t>Operational Risk</t>
+        </is>
+      </c>
+      <c r="G81" s="36" t="inlineStr">
+        <is>
+          <t>Operations</t>
+        </is>
+      </c>
+      <c r="H81" s="36" t="inlineStr">
+        <is>
+          <t>$800 million</t>
+        </is>
+      </c>
+      <c r="I81" s="37" t="n">
+        <v>800</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" s="23" t="n">
+        <v>77</v>
+      </c>
+      <c r="B82" s="16" t="inlineStr">
+        <is>
+          <t>Fortis (Belgium)</t>
+        </is>
+      </c>
+      <c r="C82" s="16" t="inlineStr">
+        <is>
+          <t>Belgium</t>
+        </is>
+      </c>
+      <c r="D82" s="23" t="n">
+        <v>2008</v>
+      </c>
+      <c r="E82" s="16" t="inlineStr">
+        <is>
+          <t>Inadequate Risk Management during ABN AMRO Acquisition</t>
+        </is>
+      </c>
+      <c r="F82" s="16" t="inlineStr">
+        <is>
+          <t>Strategic Risk</t>
+        </is>
+      </c>
+      <c r="G82" s="16" t="inlineStr">
+        <is>
+          <t>Strategic</t>
+        </is>
+      </c>
+      <c r="H82" s="16" t="inlineStr">
+        <is>
+          <t>$53 billion</t>
+        </is>
+      </c>
+      <c r="I82" s="34" t="n">
+        <v>53000</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" s="35" t="n">
+        <v>78</v>
+      </c>
+      <c r="B83" s="36" t="inlineStr">
+        <is>
+          <t>Fortis (Belgium/Netherlands)</t>
+        </is>
+      </c>
+      <c r="C83" s="36" t="inlineStr">
+        <is>
+          <t>Belgium</t>
+        </is>
+      </c>
+      <c r="D83" s="35" t="n">
+        <v>2008</v>
+      </c>
+      <c r="E83" s="36" t="inlineStr">
+        <is>
+          <t>Overexposure to Subprime Mortgage Market leading to insolvency</t>
+        </is>
+      </c>
+      <c r="F83" s="36" t="inlineStr">
+        <is>
+          <t>Credit Risk</t>
+        </is>
+      </c>
+      <c r="G83" s="36" t="inlineStr">
+        <is>
+          <t>Strategic</t>
+        </is>
+      </c>
+      <c r="H83" s="36" t="inlineStr">
+        <is>
+          <t>€23.5 billion</t>
+        </is>
+      </c>
+      <c r="I83" s="37" t="n">
+        <v>27700</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" s="23" t="n">
+        <v>79</v>
+      </c>
+      <c r="B84" s="16" t="inlineStr">
+        <is>
+          <t>Freddie Mac</t>
+        </is>
+      </c>
+      <c r="C84" s="16" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="D84" s="23" t="n">
+        <v>2003</v>
+      </c>
+      <c r="E84" s="16" t="inlineStr">
+        <is>
+          <t>Accounting Fraud</t>
+        </is>
+      </c>
+      <c r="F84" s="16" t="inlineStr">
+        <is>
+          <t>Operational Risk</t>
+        </is>
+      </c>
+      <c r="G84" s="16" t="inlineStr">
+        <is>
+          <t>Reporting</t>
+        </is>
+      </c>
+      <c r="H84" s="16" t="inlineStr">
+        <is>
+          <t>$5 billion</t>
+        </is>
+      </c>
+      <c r="I84" s="34" t="n">
+        <v>5000</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" s="35" t="n">
+        <v>80</v>
+      </c>
+      <c r="B85" s="36" t="inlineStr">
+        <is>
+          <t>Fremont General Corporation</t>
+        </is>
+      </c>
+      <c r="C85" s="36" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="D85" s="35" t="n">
+        <v>2007</v>
+      </c>
+      <c r="E85" s="36" t="inlineStr">
+        <is>
+          <t>Subprime Lending and Regulatory Issues</t>
+        </is>
+      </c>
+      <c r="F85" s="36" t="inlineStr">
+        <is>
+          <t>Credit Risk</t>
+        </is>
+      </c>
+      <c r="G85" s="36" t="inlineStr">
+        <is>
+          <t>Compliance</t>
+        </is>
+      </c>
+      <c r="H85" s="36" t="inlineStr">
+        <is>
+          <t>$6.9 billion</t>
+        </is>
+      </c>
+      <c r="I85" s="37" t="n">
+        <v>6900</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" s="23" t="n">
+        <v>81</v>
+      </c>
+      <c r="B86" s="16" t="inlineStr">
+        <is>
+          <t>Glitnir (Iceland)</t>
+        </is>
+      </c>
+      <c r="C86" s="16" t="inlineStr">
+        <is>
+          <t>Iceland</t>
+        </is>
+      </c>
+      <c r="D86" s="23" t="n">
+        <v>2008</v>
+      </c>
+      <c r="E86" s="16" t="inlineStr">
+        <is>
+          <t>Overexposure to Wholesale Funding Market</t>
+        </is>
+      </c>
+      <c r="F86" s="16" t="inlineStr">
+        <is>
+          <t>Credit Risk</t>
+        </is>
+      </c>
+      <c r="G86" s="16" t="inlineStr">
+        <is>
+          <t>Strategic</t>
+        </is>
+      </c>
+      <c r="H86" s="16" t="inlineStr">
+        <is>
+          <t>€1.6 billion</t>
+        </is>
+      </c>
+      <c r="I86" s="34" t="n">
+        <v>1900</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" s="35" t="n">
+        <v>82</v>
+      </c>
+      <c r="B87" s="36" t="inlineStr">
+        <is>
+          <t>Global Crossing</t>
+        </is>
+      </c>
+      <c r="C87" s="36" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="D87" s="35" t="n">
+        <v>2002</v>
+      </c>
+      <c r="E87" s="36" t="inlineStr">
+        <is>
+          <t>Accounting Fraud and Misrepresentation</t>
+        </is>
+      </c>
+      <c r="F87" s="36" t="inlineStr">
+        <is>
+          <t>Operational Risk</t>
+        </is>
+      </c>
+      <c r="G87" s="36" t="inlineStr">
+        <is>
+          <t>Reporting</t>
+        </is>
+      </c>
+      <c r="H87" s="36" t="inlineStr">
+        <is>
+          <t>$22.4 billion</t>
+        </is>
+      </c>
+      <c r="I87" s="37" t="n">
+        <v>22400</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" s="23" t="n">
+        <v>83</v>
+      </c>
+      <c r="B88" s="16" t="inlineStr">
+        <is>
+          <t>HBL (Pakistan)</t>
+        </is>
+      </c>
+      <c r="C88" s="16" t="inlineStr">
+        <is>
+          <t>Pakistan</t>
+        </is>
+      </c>
+      <c r="D88" s="23" t="n">
+        <v>2017</v>
+      </c>
+      <c r="E88" s="16" t="inlineStr">
+        <is>
+          <t>Money Laundering</t>
+        </is>
+      </c>
+      <c r="F88" s="16" t="inlineStr">
+        <is>
+          <t>Operational Risk</t>
+        </is>
+      </c>
+      <c r="G88" s="16" t="inlineStr">
+        <is>
+          <t>Compliance</t>
+        </is>
+      </c>
+      <c r="H88" s="16" t="inlineStr">
+        <is>
+          <t>$225 million</t>
+        </is>
+      </c>
+      <c r="I88" s="34" t="n">
+        <v>225</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" s="35" t="n">
+        <v>84</v>
+      </c>
+      <c r="B89" s="36" t="inlineStr">
+        <is>
+          <t>HBOS (UK)</t>
+        </is>
+      </c>
+      <c r="C89" s="36" t="inlineStr">
+        <is>
+          <t>United Kingdom</t>
+        </is>
+      </c>
+      <c r="D89" s="35" t="n">
+        <v>2008</v>
+      </c>
+      <c r="E89" s="36" t="inlineStr">
+        <is>
+          <t>Overexposure to Property Market leading to insolvency</t>
+        </is>
+      </c>
+      <c r="F89" s="36" t="inlineStr">
+        <is>
+          <t>Credit Risk</t>
+        </is>
+      </c>
+      <c r="G89" s="36" t="inlineStr">
+        <is>
+          <t>Strategic</t>
+        </is>
+      </c>
+      <c r="H89" s="36" t="inlineStr">
+        <is>
+          <t>£10 billion</t>
+        </is>
+      </c>
+      <c r="I89" s="37" t="n">
+        <v>13500</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" s="23" t="n">
+        <v>85</v>
+      </c>
+      <c r="B90" s="16" t="inlineStr">
+        <is>
+          <t>HealthSouth Corporation</t>
+        </is>
+      </c>
+      <c r="C90" s="16" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="D90" s="23" t="n">
+        <v>2003</v>
+      </c>
+      <c r="E90" s="16" t="inlineStr">
+        <is>
+          <t>Accounting Fraud</t>
+        </is>
+      </c>
+      <c r="F90" s="16" t="inlineStr">
+        <is>
+          <t>Operational Risk</t>
+        </is>
+      </c>
+      <c r="G90" s="16" t="inlineStr">
+        <is>
+          <t>Reporting</t>
+        </is>
+      </c>
+      <c r="H90" s="16" t="inlineStr">
+        <is>
+          <t>$2.7 billion</t>
+        </is>
+      </c>
+      <c r="I90" s="34" t="n">
+        <v>2700</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" s="35" t="n">
+        <v>86</v>
+      </c>
+      <c r="B91" s="36" t="inlineStr">
+        <is>
+          <t>HIH Insurance (Australia)</t>
+        </is>
+      </c>
+      <c r="C91" s="36" t="inlineStr">
+        <is>
+          <t>Australia</t>
+        </is>
+      </c>
+      <c r="D91" s="35" t="n">
+        <v>2001</v>
+      </c>
+      <c r="E91" s="36" t="inlineStr">
+        <is>
+          <t>Fraud and Inadequate Risk Management</t>
+        </is>
+      </c>
+      <c r="F91" s="36" t="inlineStr">
+        <is>
+          <t>Operational Risk</t>
+        </is>
+      </c>
+      <c r="G91" s="36" t="inlineStr">
+        <is>
+          <t>Operations</t>
+        </is>
+      </c>
+      <c r="H91" s="36" t="inlineStr">
+        <is>
+          <t>$5.3 billion AUD</t>
+        </is>
+      </c>
+      <c r="I91" s="37" t="n">
+        <v>5300</v>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" s="23" t="n">
+        <v>87</v>
+      </c>
+      <c r="B92" s="16" t="inlineStr">
+        <is>
+          <t>HSBC</t>
+        </is>
+      </c>
+      <c r="C92" s="16" t="inlineStr">
+        <is>
+          <t>United Kingdom</t>
+        </is>
+      </c>
+      <c r="D92" s="23" t="n">
+        <v>2012</v>
+      </c>
+      <c r="E92" s="16" t="inlineStr">
+        <is>
+          <t>Money Laundering and Sanctions Breaching</t>
+        </is>
+      </c>
+      <c r="F92" s="16" t="inlineStr">
+        <is>
+          <t>Operational Risk</t>
+        </is>
+      </c>
+      <c r="G92" s="16" t="inlineStr">
+        <is>
+          <t>Compliance</t>
+        </is>
+      </c>
+      <c r="H92" s="16" t="inlineStr">
+        <is>
+          <t>$1.9 billion</t>
+        </is>
+      </c>
+      <c r="I92" s="34" t="n">
+        <v>1900</v>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" s="35" t="n">
+        <v>88</v>
+      </c>
+      <c r="B93" s="36" t="inlineStr">
+        <is>
+          <t>HSH Nordbank (Germany)</t>
+        </is>
+      </c>
+      <c r="C93" s="36" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="D93" s="35" t="n">
+        <v>2008</v>
+      </c>
+      <c r="E93" s="36" t="inlineStr">
+        <is>
+          <t>Overexposure to Subprime Mortgages and Shipping Loans</t>
+        </is>
+      </c>
+      <c r="F93" s="36" t="inlineStr">
+        <is>
+          <t>Credit Risk</t>
+        </is>
+      </c>
+      <c r="G93" s="36" t="inlineStr">
+        <is>
+          <t>Strategic</t>
+        </is>
+      </c>
+      <c r="H93" s="36" t="inlineStr">
+        <is>
+          <t>€2 billion</t>
+        </is>
+      </c>
+      <c r="I93" s="37" t="n">
+        <v>2400</v>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" s="23" t="n">
+        <v>89</v>
+      </c>
+      <c r="B94" s="16" t="inlineStr">
+        <is>
+          <t>Hwang's Archegos Capital Management</t>
+        </is>
+      </c>
+      <c r="C94" s="16" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="D94" s="23" t="n">
+        <v>2021</v>
+      </c>
+      <c r="E94" s="16" t="inlineStr">
+        <is>
+          <t>Uncontrolled Leverage and Concentration Risk</t>
+        </is>
+      </c>
+      <c r="F94" s="16" t="inlineStr">
+        <is>
+          <t>Market Risk</t>
+        </is>
+      </c>
+      <c r="G94" s="16" t="inlineStr">
+        <is>
+          <t>Operations</t>
+        </is>
+      </c>
+      <c r="H94" s="16" t="inlineStr">
+        <is>
+          <t>$20 billion</t>
+        </is>
+      </c>
+      <c r="I94" s="34" t="n">
+        <v>20000</v>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" s="35" t="n">
+        <v>90</v>
+      </c>
+      <c r="B95" s="36" t="inlineStr">
+        <is>
+          <t>Hypo Alpe-Adria-Bank International (Austria)</t>
+        </is>
+      </c>
+      <c r="C95" s="36" t="inlineStr">
+        <is>
+          <t>Austria</t>
+        </is>
+      </c>
+      <c r="D95" s="35" t="n">
+        <v>2009</v>
+      </c>
+      <c r="E95" s="36" t="inlineStr">
+        <is>
+          <t>Rapid Expansion and Overexposure to Balkans Real Estate Market</t>
+        </is>
+      </c>
+      <c r="F95" s="36" t="inlineStr">
+        <is>
+          <t>Credit Risk</t>
+        </is>
+      </c>
+      <c r="G95" s="36" t="inlineStr">
+        <is>
+          <t>Strategic</t>
+        </is>
+      </c>
+      <c r="H95" s="36" t="inlineStr">
+        <is>
+          <t>€7.6 billion</t>
+        </is>
+      </c>
+      <c r="I95" s="37" t="n">
+        <v>9000</v>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" s="23" t="n">
+        <v>91</v>
+      </c>
+      <c r="B96" s="16" t="inlineStr">
+        <is>
+          <t>Hypo Real Estate (Germany)</t>
+        </is>
+      </c>
+      <c r="C96" s="16" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="D96" s="23" t="n">
+        <v>2008</v>
+      </c>
+      <c r="E96" s="16" t="inlineStr">
+        <is>
+          <t>Overexposure to Mortgage Backed Securities</t>
+        </is>
+      </c>
+      <c r="F96" s="16" t="inlineStr">
+        <is>
+          <t>Credit Risk</t>
+        </is>
+      </c>
+      <c r="G96" s="16" t="inlineStr">
+        <is>
+          <t>Strategic</t>
+        </is>
+      </c>
+      <c r="H96" s="16" t="inlineStr">
+        <is>
+          <t>€10 billion</t>
+        </is>
+      </c>
+      <c r="I96" s="34" t="n">
+        <v>11800</v>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" s="35" t="n">
+        <v>92</v>
+      </c>
+      <c r="B97" s="36" t="inlineStr">
+        <is>
+          <t>Hypo Real Estate (Germany)</t>
+        </is>
+      </c>
+      <c r="C97" s="36" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="D97" s="35" t="n">
+        <v>2008</v>
+      </c>
+      <c r="E97" s="36" t="inlineStr">
+        <is>
+          <t>Overexposure to Mortgage-Backed Securities leading to insolvency</t>
+        </is>
+      </c>
+      <c r="F97" s="36" t="inlineStr">
+        <is>
+          <t>Credit Risk</t>
+        </is>
+      </c>
+      <c r="G97" s="36" t="inlineStr">
+        <is>
+          <t>Strategic</t>
+        </is>
+      </c>
+      <c r="H97" s="36" t="inlineStr">
+        <is>
+          <t>$64.48 billion</t>
+        </is>
+      </c>
+      <c r="I97" s="37" t="n">
+        <v>64500</v>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" s="23" t="n">
+        <v>93</v>
+      </c>
+      <c r="B98" s="16" t="inlineStr">
+        <is>
+          <t>ICBC (China)</t>
+        </is>
+      </c>
+      <c r="C98" s="16" t="inlineStr">
+        <is>
+          <t>China</t>
+        </is>
+      </c>
+      <c r="D98" s="23" t="n">
+        <v>2020</v>
+      </c>
+      <c r="E98" s="16" t="inlineStr">
+        <is>
+          <t>Overexposure to Bad Loans</t>
+        </is>
+      </c>
+      <c r="F98" s="16" t="inlineStr">
+        <is>
+          <t>Credit Risk</t>
+        </is>
+      </c>
+      <c r="G98" s="16" t="inlineStr">
+        <is>
+          <t>Strategic</t>
+        </is>
+      </c>
+      <c r="H98" s="16" t="inlineStr">
+        <is>
+          <t>CNY 45.6 billion</t>
+        </is>
+      </c>
+      <c r="I98" s="34" t="n">
+        <v>6800</v>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" s="35" t="n">
+        <v>94</v>
+      </c>
+      <c r="B99" s="36" t="inlineStr">
+        <is>
+          <t>Icelandic Banks (Kaupthing, Landsbanki, Glitnir)</t>
+        </is>
+      </c>
+      <c r="C99" s="36" t="inlineStr">
+        <is>
+          <t>Iceland</t>
+        </is>
+      </c>
+      <c r="D99" s="35" t="n">
+        <v>2008</v>
+      </c>
+      <c r="E99" s="36" t="inlineStr">
+        <is>
+          <t>Overexpansion and Overexposure to Financial Market</t>
+        </is>
+      </c>
+      <c r="F99" s="36" t="inlineStr">
+        <is>
+          <t>Credit Risk</t>
+        </is>
+      </c>
+      <c r="G99" s="36" t="inlineStr">
+        <is>
+          <t>Strategic</t>
+        </is>
+      </c>
+      <c r="H99" s="36" t="inlineStr">
+        <is>
+          <t>$85 billion</t>
+        </is>
+      </c>
+      <c r="I99" s="37" t="n">
+        <v>85000</v>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" s="23" t="n">
+        <v>95</v>
+      </c>
+      <c r="B100" s="16" t="inlineStr">
+        <is>
+          <t>Icesave (Iceland)</t>
+        </is>
+      </c>
+      <c r="C100" s="16" t="inlineStr">
+        <is>
+          <t>Iceland</t>
+        </is>
+      </c>
+      <c r="D100" s="23" t="n">
+        <v>2008</v>
+      </c>
+      <c r="E100" s="16" t="inlineStr">
+        <is>
+          <t>Overexposure to Wholesale Funding Market</t>
+        </is>
+      </c>
+      <c r="F100" s="16" t="inlineStr">
+        <is>
+          <t>Credit Risk</t>
+        </is>
+      </c>
+      <c r="G100" s="16" t="inlineStr">
+        <is>
+          <t>Strategic</t>
+        </is>
+      </c>
+      <c r="H100" s="16" t="inlineStr">
+        <is>
+          <t>£4.5 billion</t>
+        </is>
+      </c>
+      <c r="I100" s="34" t="n">
+        <v>6100</v>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" s="35" t="n">
+        <v>96</v>
+      </c>
+      <c r="B101" s="36" t="inlineStr">
+        <is>
+          <t>IndyMac Bancorp</t>
+        </is>
+      </c>
+      <c r="C101" s="36" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="D101" s="35" t="n">
+        <v>2008</v>
+      </c>
+      <c r="E101" s="36" t="inlineStr">
+        <is>
+          <t>Overexposure to Alt-A Loans</t>
+        </is>
+      </c>
+      <c r="F101" s="36" t="inlineStr">
+        <is>
+          <t>Credit Risk</t>
+        </is>
+      </c>
+      <c r="G101" s="36" t="inlineStr">
+        <is>
+          <t>Strategic</t>
+        </is>
+      </c>
+      <c r="H101" s="36" t="inlineStr">
+        <is>
+          <t>$10.7 billion</t>
+        </is>
+      </c>
+      <c r="I101" s="37" t="n">
+        <v>10700</v>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" s="23" t="n">
+        <v>97</v>
+      </c>
+      <c r="B102" s="16" t="inlineStr">
+        <is>
+          <t>Irish Life and Permanent (Ireland)</t>
+        </is>
+      </c>
+      <c r="C102" s="16" t="inlineStr">
+        <is>
+          <t>Ireland</t>
+        </is>
+      </c>
+      <c r="D102" s="23" t="n">
+        <v>2010</v>
+      </c>
+      <c r="E102" s="16" t="inlineStr">
+        <is>
+          <t>Overexposure to Property Loans</t>
+        </is>
+      </c>
+      <c r="F102" s="16" t="inlineStr">
+        <is>
+          <t>Credit Risk</t>
+        </is>
+      </c>
+      <c r="G102" s="16" t="inlineStr">
+        <is>
+          <t>Reporting</t>
+        </is>
+      </c>
+      <c r="H102" s="16" t="inlineStr">
+        <is>
+          <t>€4 billion</t>
+        </is>
+      </c>
+      <c r="I102" s="34" t="n">
+        <v>4700</v>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" s="35" t="n">
+        <v>98</v>
+      </c>
+      <c r="B103" s="36" t="inlineStr">
+        <is>
+          <t>Irish Nationwide Building Society (Ireland)</t>
+        </is>
+      </c>
+      <c r="C103" s="36" t="inlineStr">
+        <is>
+          <t>Ireland</t>
+        </is>
+      </c>
+      <c r="D103" s="35" t="n">
+        <v>2010</v>
+      </c>
+      <c r="E103" s="36" t="inlineStr">
+        <is>
+          <t>Overexposure to Commercial Property Loans</t>
+        </is>
+      </c>
+      <c r="F103" s="36" t="inlineStr">
+        <is>
+          <t>Credit Risk</t>
+        </is>
+      </c>
+      <c r="G103" s="36" t="inlineStr">
+        <is>
+          <t>Operations</t>
+        </is>
+      </c>
+      <c r="H103" s="36" t="inlineStr">
+        <is>
+          <t>€5.4 billion</t>
+        </is>
+      </c>
+      <c r="I103" s="37" t="n">
+        <v>6400</v>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" s="23" t="n">
+        <v>99</v>
+      </c>
+      <c r="B104" s="16" t="inlineStr">
+        <is>
+          <t>Irwin Financial Corporation</t>
+        </is>
+      </c>
+      <c r="C104" s="16" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="D104" s="23" t="n">
+        <v>2009</v>
+      </c>
+      <c r="E104" s="16" t="inlineStr">
+        <is>
+          <t>Overexposure to Home Equity Loans</t>
+        </is>
+      </c>
+      <c r="F104" s="16" t="inlineStr">
+        <is>
+          <t>Credit Risk</t>
+        </is>
+      </c>
+      <c r="G104" s="16" t="inlineStr">
+        <is>
+          <t>Strategic</t>
+        </is>
+      </c>
+      <c r="H104" s="16" t="inlineStr">
+        <is>
+          <t>$1 billion</t>
+        </is>
+      </c>
+      <c r="I104" s="34" t="n">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" s="35" t="n">
+        <v>100</v>
+      </c>
+      <c r="B105" s="36" t="inlineStr">
+        <is>
+          <t>JPMorgan Chase (London Whale)</t>
+        </is>
+      </c>
+      <c r="C105" s="36" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="D105" s="35" t="n">
+        <v>2012</v>
+      </c>
+      <c r="E105" s="36" t="inlineStr">
+        <is>
+          <t>Poorly Supervised Proprietary Trading</t>
+        </is>
+      </c>
+      <c r="F105" s="36" t="inlineStr">
+        <is>
+          <t>Market Risk</t>
+        </is>
+      </c>
+      <c r="G105" s="36" t="inlineStr">
+        <is>
+          <t>Operations</t>
+        </is>
+      </c>
+      <c r="H105" s="36" t="inlineStr">
+        <is>
+          <t>$6.2 billion</t>
+        </is>
+      </c>
+      <c r="I105" s="37" t="n">
+        <v>6200</v>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" s="23" t="n">
+        <v>101</v>
+      </c>
+      <c r="B106" s="16" t="inlineStr">
+        <is>
+          <t>Kaupthing (Iceland)</t>
+        </is>
+      </c>
+      <c r="C106" s="16" t="inlineStr">
+        <is>
+          <t>Iceland</t>
+        </is>
+      </c>
+      <c r="D106" s="23" t="n">
+        <v>2008</v>
+      </c>
+      <c r="E106" s="16" t="inlineStr">
+        <is>
+          <t>Overexposure to Wholesale Funding Market</t>
+        </is>
+      </c>
+      <c r="F106" s="16" t="inlineStr">
+        <is>
+          <t>Credit Risk</t>
+        </is>
+      </c>
+      <c r="G106" s="16" t="inlineStr">
+        <is>
+          <t>Strategic</t>
+        </is>
+      </c>
+      <c r="H106" s="16" t="inlineStr">
+        <is>
+          <t>€5.5 billion</t>
+        </is>
+      </c>
+      <c r="I106" s="34" t="n">
+        <v>6500</v>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" s="35" t="n">
+        <v>102</v>
+      </c>
+      <c r="B107" s="36" t="inlineStr">
+        <is>
+          <t>Kaupthing Bank (Iceland)</t>
+        </is>
+      </c>
+      <c r="C107" s="36" t="inlineStr">
+        <is>
+          <t>Iceland</t>
+        </is>
+      </c>
+      <c r="D107" s="35" t="n">
+        <v>2008</v>
+      </c>
+      <c r="E107" s="36" t="inlineStr">
+        <is>
+          <t>Overexpansion and Insufficient Capital</t>
+        </is>
+      </c>
+      <c r="F107" s="36" t="inlineStr">
+        <is>
+          <t>Strategic Risk</t>
+        </is>
+      </c>
+      <c r="G107" s="36" t="inlineStr">
+        <is>
+          <t>Strategic</t>
+        </is>
+      </c>
+      <c r="H107" s="36" t="inlineStr">
+        <is>
+          <t>$50 billion</t>
+        </is>
+      </c>
+      <c r="I107" s="37" t="n">
+        <v>50000</v>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" s="23" t="n">
+        <v>103</v>
+      </c>
+      <c r="B108" s="16" t="inlineStr">
+        <is>
+          <t>Knight Capital (US)</t>
+        </is>
+      </c>
+      <c r="C108" s="16" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="D108" s="23" t="n">
+        <v>2012</v>
+      </c>
+      <c r="E108" s="16" t="inlineStr">
+        <is>
+          <t>Software Glitch in Trading Algorithm</t>
+        </is>
+      </c>
+      <c r="F108" s="16" t="inlineStr">
+        <is>
+          <t>Market Risk</t>
+        </is>
+      </c>
+      <c r="G108" s="16" t="inlineStr">
+        <is>
+          <t>Operations</t>
+        </is>
+      </c>
+      <c r="H108" s="16" t="inlineStr">
+        <is>
+          <t>$460 million</t>
+        </is>
+      </c>
+      <c r="I108" s="34" t="n">
+        <v>460</v>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" s="35" t="n">
+        <v>104</v>
+      </c>
+      <c r="B109" s="36" t="inlineStr">
+        <is>
+          <t>Kreditanstalt (Austria)</t>
+        </is>
+      </c>
+      <c r="C109" s="36" t="inlineStr">
+        <is>
+          <t>Austria</t>
+        </is>
+      </c>
+      <c r="D109" s="35" t="n">
+        <v>1931</v>
+      </c>
+      <c r="E109" s="36" t="inlineStr">
+        <is>
+          <t>Overexposure to Post-War German and Central European Debt</t>
+        </is>
+      </c>
+      <c r="F109" s="36" t="inlineStr">
+        <is>
+          <t>Credit Risk</t>
+        </is>
+      </c>
+      <c r="G109" s="36" t="inlineStr">
+        <is>
+          <t>Strategic</t>
+        </is>
+      </c>
+      <c r="H109" s="36" t="inlineStr">
+        <is>
+          <t>$7.6 billion</t>
+        </is>
+      </c>
+      <c r="I109" s="37" t="n">
+        <v>7600</v>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" s="23" t="n">
+        <v>105</v>
+      </c>
+      <c r="B110" s="16" t="inlineStr">
+        <is>
+          <t>Laiki Bank (Cyprus)</t>
+        </is>
+      </c>
+      <c r="C110" s="16" t="inlineStr">
+        <is>
+          <t>Cyprus</t>
+        </is>
+      </c>
+      <c r="D110" s="23" t="n">
+        <v>2013</v>
+      </c>
+      <c r="E110" s="16" t="inlineStr">
+        <is>
+          <t>Insolvency due to overexposure to Greek debt</t>
+        </is>
+      </c>
+      <c r="F110" s="16" t="inlineStr">
+        <is>
+          <t>Credit Risk</t>
+        </is>
+      </c>
+      <c r="G110" s="16" t="inlineStr">
+        <is>
+          <t>Strategic</t>
+        </is>
+      </c>
+      <c r="H110" s="16" t="inlineStr">
+        <is>
+          <t>€4.5 billion</t>
+        </is>
+      </c>
+      <c r="I110" s="34" t="n">
+        <v>5300</v>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" s="35" t="n">
+        <v>106</v>
+      </c>
+      <c r="B111" s="36" t="inlineStr">
+        <is>
+          <t>Landesbank Sachsen (Germany)</t>
+        </is>
+      </c>
+      <c r="C111" s="36" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="D111" s="35" t="n">
+        <v>2007</v>
+      </c>
+      <c r="E111" s="36" t="inlineStr">
+        <is>
+          <t>Overexposure to Structured Investment Vehicles leading to insolvency</t>
+        </is>
+      </c>
+      <c r="F111" s="36" t="inlineStr">
+        <is>
+          <t>Credit Risk</t>
+        </is>
+      </c>
+      <c r="G111" s="36" t="inlineStr">
+        <is>
+          <t>Strategic</t>
+        </is>
+      </c>
+      <c r="H111" s="36" t="inlineStr">
+        <is>
+          <t>€17 billion</t>
+        </is>
+      </c>
+      <c r="I111" s="37" t="n">
+        <v>20100</v>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" s="23" t="n">
+        <v>107</v>
+      </c>
+      <c r="B112" s="16" t="inlineStr">
+        <is>
+          <t>Landsbanki (Iceland)</t>
+        </is>
+      </c>
+      <c r="C112" s="16" t="inlineStr">
+        <is>
+          <t>Iceland</t>
+        </is>
+      </c>
+      <c r="D112" s="23" t="n">
+        <v>2008</v>
+      </c>
+      <c r="E112" s="16" t="inlineStr">
+        <is>
+          <t>Overexposure to Wholesale Funding Market</t>
+        </is>
+      </c>
+      <c r="F112" s="16" t="inlineStr">
+        <is>
+          <t>Credit Risk</t>
+        </is>
+      </c>
+      <c r="G112" s="16" t="inlineStr">
+        <is>
+          <t>Strategic</t>
+        </is>
+      </c>
+      <c r="H112" s="16" t="inlineStr">
+        <is>
+          <t>€2.2 billion</t>
+        </is>
+      </c>
+      <c r="I112" s="34" t="n">
+        <v>2600</v>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" s="35" t="n">
+        <v>108</v>
+      </c>
+      <c r="B113" s="36" t="inlineStr">
+        <is>
+          <t>Lehman Brothers</t>
+        </is>
+      </c>
+      <c r="C113" s="36" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="D113" s="35" t="n">
+        <v>2008</v>
+      </c>
+      <c r="E113" s="36" t="inlineStr">
+        <is>
+          <t>Overexposure to Subprime Mortgages</t>
+        </is>
+      </c>
+      <c r="F113" s="36" t="inlineStr">
+        <is>
+          <t>Credit Risk</t>
+        </is>
+      </c>
+      <c r="G113" s="36" t="inlineStr">
+        <is>
+          <t>Strategic</t>
+        </is>
+      </c>
+      <c r="H113" s="36" t="inlineStr">
+        <is>
+          <t>$30 billion</t>
+        </is>
+      </c>
+      <c r="I113" s="37" t="n">
+        <v>30000</v>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" s="23" t="n">
+        <v>109</v>
+      </c>
+      <c r="B114" s="16" t="inlineStr">
+        <is>
+          <t>Lincoln Savings and Loan</t>
+        </is>
+      </c>
+      <c r="C114" s="16" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="D114" s="23" t="n">
+        <v>1989</v>
+      </c>
+      <c r="E114" s="16" t="inlineStr">
+        <is>
+          <t>Fraudulent Business Practices and Regulatory Capture</t>
+        </is>
+      </c>
+      <c r="F114" s="16" t="inlineStr">
+        <is>
+          <t>Operational Risk</t>
+        </is>
+      </c>
+      <c r="G114" s="16" t="inlineStr">
+        <is>
+          <t>Compliance</t>
+        </is>
+      </c>
+      <c r="H114" s="16" t="inlineStr">
+        <is>
+          <t>$3.4 billion</t>
+        </is>
+      </c>
+      <c r="I114" s="34" t="n">
+        <v>3400</v>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" s="35" t="n">
+        <v>110</v>
+      </c>
+      <c r="B115" s="36" t="inlineStr">
+        <is>
+          <t>Lloyd's of London (UK)</t>
+        </is>
+      </c>
+      <c r="C115" s="36" t="inlineStr">
+        <is>
+          <t>United Kingdom</t>
+        </is>
+      </c>
+      <c r="D115" s="35" t="n">
+        <v>2001</v>
+      </c>
+      <c r="E115" s="36" t="inlineStr">
+        <is>
+          <t>World Trade Center Insurance Dispute</t>
+        </is>
+      </c>
+      <c r="F115" s="36" t="inlineStr">
+        <is>
+          <t>Strategic Risk</t>
+        </is>
+      </c>
+      <c r="G115" s="36" t="inlineStr">
+        <is>
+          <t>Strategic</t>
+        </is>
+      </c>
+      <c r="H115" s="36" t="inlineStr">
+        <is>
+          <t>$5.6 billion</t>
+        </is>
+      </c>
+      <c r="I115" s="37" t="n">
+        <v>5600</v>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" s="23" t="n">
+        <v>111</v>
+      </c>
+      <c r="B116" s="16" t="inlineStr">
+        <is>
+          <t>Lloyds Banking Group (UK)</t>
+        </is>
+      </c>
+      <c r="C116" s="16" t="inlineStr">
+        <is>
+          <t>United Kingdom</t>
+        </is>
+      </c>
+      <c r="D116" s="23" t="n">
+        <v>2013</v>
+      </c>
+      <c r="E116" s="16" t="inlineStr">
+        <is>
+          <t>Payment Protection Insurance (PPI) Mis-selling</t>
+        </is>
+      </c>
+      <c r="F116" s="16" t="inlineStr">
+        <is>
+          <t>Conduct Risk</t>
+        </is>
+      </c>
+      <c r="G116" s="16" t="inlineStr">
+        <is>
+          <t>Compliance</t>
+        </is>
+      </c>
+      <c r="H116" s="16" t="inlineStr">
+        <is>
+          <t>£22 billion</t>
+        </is>
+      </c>
+      <c r="I116" s="34" t="n">
+        <v>29700</v>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" s="35" t="n">
+        <v>112</v>
+      </c>
+      <c r="B117" s="36" t="inlineStr">
+        <is>
+          <t>Long-Term Capital Management</t>
+        </is>
+      </c>
+      <c r="C117" s="36" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="D117" s="35" t="n">
+        <v>1998</v>
+      </c>
+      <c r="E117" s="36" t="inlineStr">
+        <is>
+          <t>High Leverage and Market Risk</t>
+        </is>
+      </c>
+      <c r="F117" s="36" t="inlineStr">
+        <is>
+          <t>Market Risk</t>
+        </is>
+      </c>
+      <c r="G117" s="36" t="inlineStr">
+        <is>
+          <t>Strategic</t>
+        </is>
+      </c>
+      <c r="H117" s="36" t="inlineStr">
+        <is>
+          <t>$4.6 billion</t>
+        </is>
+      </c>
+      <c r="I117" s="37" t="n">
+        <v>4600</v>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" s="23" t="n">
+        <v>113</v>
+      </c>
+      <c r="B118" s="16" t="inlineStr">
+        <is>
+          <t>Luckin Coffee (China)</t>
+        </is>
+      </c>
+      <c r="C118" s="16" t="inlineStr">
+        <is>
+          <t>China</t>
+        </is>
+      </c>
+      <c r="D118" s="23" t="n">
+        <v>2020</v>
+      </c>
+      <c r="E118" s="16" t="inlineStr">
+        <is>
+          <t>Accounting Fraud</t>
+        </is>
+      </c>
+      <c r="F118" s="16" t="inlineStr">
+        <is>
+          <t>Operational Risk</t>
+        </is>
+      </c>
+      <c r="G118" s="16" t="inlineStr">
+        <is>
+          <t>Reporting</t>
+        </is>
+      </c>
+      <c r="H118" s="16" t="inlineStr">
+        <is>
+          <t>$310 million</t>
+        </is>
+      </c>
+      <c r="I118" s="34" t="n">
+        <v>310</v>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" s="35" t="n">
+        <v>114</v>
+      </c>
+      <c r="B119" s="36" t="inlineStr">
+        <is>
+          <t>Maybank (Malaysia)</t>
+        </is>
+      </c>
+      <c r="C119" s="36" t="inlineStr">
+        <is>
+          <t>Malaysia</t>
+        </is>
+      </c>
+      <c r="D119" s="35" t="n">
+        <v>2015</v>
+      </c>
+      <c r="E119" s="36" t="inlineStr">
+        <is>
+          <t>Overexposure to Oil and Gas Sector</t>
+        </is>
+      </c>
+      <c r="F119" s="36" t="inlineStr">
+        <is>
+          <t>Credit Risk</t>
+        </is>
+      </c>
+      <c r="G119" s="36" t="inlineStr">
+        <is>
+          <t>Strategic</t>
+        </is>
+      </c>
+      <c r="H119" s="36" t="inlineStr">
+        <is>
+          <t>MYR 1.74 billion</t>
+        </is>
+      </c>
+      <c r="I119" s="37" t="n">
+        <v>418</v>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" s="23" t="n">
+        <v>115</v>
+      </c>
+      <c r="B120" s="16" t="inlineStr">
+        <is>
+          <t>Merrill Lynch</t>
+        </is>
+      </c>
+      <c r="C120" s="16" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="D120" s="23" t="n">
+        <v>2008</v>
+      </c>
+      <c r="E120" s="16" t="inlineStr">
+        <is>
+          <t>Overexposure to Subprime Mortgages</t>
+        </is>
+      </c>
+      <c r="F120" s="16" t="inlineStr">
+        <is>
+          <t>Credit Risk</t>
+        </is>
+      </c>
+      <c r="G120" s="16" t="inlineStr">
+        <is>
+          <t>Strategic</t>
+        </is>
+      </c>
+      <c r="H120" s="16" t="inlineStr">
+        <is>
+          <t>$51.8 billion</t>
+        </is>
+      </c>
+      <c r="I120" s="34" t="n">
+        <v>51800</v>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" s="35" t="n">
+        <v>116</v>
+      </c>
+      <c r="B121" s="36" t="inlineStr">
+        <is>
+          <t>Metropolitan Life Insurance Company</t>
+        </is>
+      </c>
+      <c r="C121" s="36" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="D121" s="35" t="n">
+        <v>1999</v>
+      </c>
+      <c r="E121" s="36" t="inlineStr">
+        <is>
+          <t>Misrepresentation of Insurance Products</t>
+        </is>
+      </c>
+      <c r="F121" s="36" t="inlineStr">
+        <is>
+          <t>Operational Risk</t>
+        </is>
+      </c>
+      <c r="G121" s="36" t="inlineStr">
+        <is>
+          <t>Compliance</t>
+        </is>
+      </c>
+      <c r="H121" s="36" t="inlineStr">
+        <is>
+          <t>$1.6 billion</t>
+        </is>
+      </c>
+      <c r="I121" s="37" t="n">
+        <v>1600</v>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" s="23" t="n">
+        <v>117</v>
+      </c>
+      <c r="B122" s="16" t="inlineStr">
+        <is>
+          <t>MF Global</t>
+        </is>
+      </c>
+      <c r="C122" s="16" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="D122" s="23" t="n">
+        <v>2011</v>
+      </c>
+      <c r="E122" s="16" t="inlineStr">
+        <is>
+          <t>Mismanagement of Funds</t>
+        </is>
+      </c>
+      <c r="F122" s="16" t="inlineStr">
+        <is>
+          <t>Operational Risk</t>
+        </is>
+      </c>
+      <c r="G122" s="16" t="inlineStr">
+        <is>
+          <t>Operations</t>
+        </is>
+      </c>
+      <c r="H122" s="16" t="inlineStr">
+        <is>
+          <t>$40 billion</t>
+        </is>
+      </c>
+      <c r="I122" s="34" t="n">
+        <v>40000</v>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" s="35" t="n">
+        <v>118</v>
+      </c>
+      <c r="B123" s="36" t="inlineStr">
+        <is>
+          <t>MF Global</t>
+        </is>
+      </c>
+      <c r="C123" s="36" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="D123" s="35" t="n">
+        <v>2011</v>
+      </c>
+      <c r="E123" s="36" t="inlineStr">
+        <is>
+          <t>Overexposure to European Sovereign Debt</t>
+        </is>
+      </c>
+      <c r="F123" s="36" t="inlineStr">
+        <is>
+          <t>Credit Risk</t>
+        </is>
+      </c>
+      <c r="G123" s="36" t="inlineStr">
+        <is>
+          <t>Strategic</t>
+        </is>
+      </c>
+      <c r="H123" s="36" t="inlineStr">
+        <is>
+          <t>$1.6 billion</t>
+        </is>
+      </c>
+      <c r="I123" s="37" t="n">
+        <v>1600</v>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" s="23" t="n">
+        <v>119</v>
+      </c>
+      <c r="B124" s="16" t="inlineStr">
+        <is>
+          <t>Monte dei Paschi (Italy)</t>
+        </is>
+      </c>
+      <c r="C124" s="16" t="inlineStr">
+        <is>
+          <t>Italy</t>
+        </is>
+      </c>
+      <c r="D124" s="23" t="n">
+        <v>2013</v>
+      </c>
+      <c r="E124" s="16" t="inlineStr">
+        <is>
+          <t>Derivative and Accounting Scandal</t>
+        </is>
+      </c>
+      <c r="F124" s="16" t="inlineStr">
+        <is>
+          <t>Conduct Risk</t>
+        </is>
+      </c>
+      <c r="G124" s="16" t="inlineStr">
+        <is>
+          <t>Reporting</t>
+        </is>
+      </c>
+      <c r="H124" s="16" t="inlineStr">
+        <is>
+          <t>€3.9 billion</t>
+        </is>
+      </c>
+      <c r="I124" s="34" t="n">
+        <v>4600</v>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" s="35" t="n">
+        <v>120</v>
+      </c>
+      <c r="B125" s="36" t="inlineStr">
+        <is>
+          <t>NAB (Australia)</t>
+        </is>
+      </c>
+      <c r="C125" s="36" t="inlineStr">
+        <is>
+          <t>Australia</t>
+        </is>
+      </c>
+      <c r="D125" s="35" t="n">
+        <v>2020</v>
+      </c>
+      <c r="E125" s="36" t="inlineStr">
+        <is>
+          <t>Money Laundering</t>
+        </is>
+      </c>
+      <c r="F125" s="36" t="inlineStr">
+        <is>
+          <t>Operational Risk</t>
+        </is>
+      </c>
+      <c r="G125" s="36" t="inlineStr">
+        <is>
+          <t>Compliance</t>
+        </is>
+      </c>
+      <c r="H125" s="36" t="inlineStr">
+        <is>
+          <t>AUD 15 million</t>
+        </is>
+      </c>
+      <c r="I125" s="37" t="n">
+        <v>10.8</v>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" s="23" t="n">
+        <v>121</v>
+      </c>
+      <c r="B126" s="16" t="inlineStr">
+        <is>
+          <t>National Century Financial Enterprises (US)</t>
+        </is>
+      </c>
+      <c r="C126" s="16" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="D126" s="23" t="n">
+        <v>2002</v>
+      </c>
+      <c r="E126" s="16" t="inlineStr">
+        <is>
+          <t>Corporate Fraud</t>
+        </is>
+      </c>
+      <c r="F126" s="16" t="inlineStr">
+        <is>
+          <t>Operational Risk</t>
+        </is>
+      </c>
+      <c r="G126" s="16" t="inlineStr">
+        <is>
+          <t>Operations</t>
+        </is>
+      </c>
+      <c r="H126" s="16" t="inlineStr">
+        <is>
+          <t>$2.6 billion</t>
+        </is>
+      </c>
+      <c r="I126" s="34" t="n">
+        <v>2600</v>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" s="35" t="n">
+        <v>122</v>
+      </c>
+      <c r="B127" s="36" t="inlineStr">
+        <is>
+          <t>New Century Financial Corporation</t>
+        </is>
+      </c>
+      <c r="C127" s="36" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="D127" s="35" t="n">
+        <v>2007</v>
+      </c>
+      <c r="E127" s="36" t="inlineStr">
+        <is>
+          <t>Overexposure to Subprime Mortgages</t>
+        </is>
+      </c>
+      <c r="F127" s="36" t="inlineStr">
+        <is>
+          <t>Credit Risk</t>
+        </is>
+      </c>
+      <c r="G127" s="36" t="inlineStr">
+        <is>
+          <t>Strategic</t>
+        </is>
+      </c>
+      <c r="H127" s="36" t="inlineStr">
+        <is>
+          <t>$1.2 billion</t>
+        </is>
+      </c>
+      <c r="I127" s="37" t="n">
+        <v>1200</v>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" s="23" t="n">
+        <v>123</v>
+      </c>
+      <c r="B128" s="16" t="inlineStr">
+        <is>
+          <t>NMC Health (UAE)</t>
+        </is>
+      </c>
+      <c r="C128" s="16" t="inlineStr">
+        <is>
+          <t>United Arab Emirates</t>
+        </is>
+      </c>
+      <c r="D128" s="23" t="n">
+        <v>2019</v>
+      </c>
+      <c r="E128" s="16" t="inlineStr">
+        <is>
+          <t>Accounting Fraud and Debt Concealment</t>
+        </is>
+      </c>
+      <c r="F128" s="16" t="inlineStr">
+        <is>
+          <t>Operational Risk</t>
+        </is>
+      </c>
+      <c r="G128" s="16" t="inlineStr">
+        <is>
+          <t>Reporting</t>
+        </is>
+      </c>
+      <c r="H128" s="16" t="inlineStr">
+        <is>
+          <t>$4 billion</t>
+        </is>
+      </c>
+      <c r="I128" s="34" t="n">
+        <v>4000</v>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" s="35" t="n">
+        <v>124</v>
+      </c>
+      <c r="B129" s="36" t="inlineStr">
+        <is>
+          <t>Nordea Bank (Sweden)</t>
+        </is>
+      </c>
+      <c r="C129" s="36" t="inlineStr">
+        <is>
+          <t>Sweden</t>
+        </is>
+      </c>
+      <c r="D129" s="35" t="n">
+        <v>2019</v>
+      </c>
+      <c r="E129" s="36" t="inlineStr">
+        <is>
+          <t>Money Laundering</t>
+        </is>
+      </c>
+      <c r="F129" s="36" t="inlineStr">
+        <is>
+          <t>Operational Risk</t>
+        </is>
+      </c>
+      <c r="G129" s="36" t="inlineStr">
+        <is>
+          <t>Compliance</t>
+        </is>
+      </c>
+      <c r="H129" s="36" t="inlineStr">
+        <is>
+          <t>SEK 4 billion</t>
+        </is>
+      </c>
+      <c r="I129" s="37" t="n">
+        <v>440</v>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" s="23" t="n">
+        <v>125</v>
+      </c>
+      <c r="B130" s="16" t="inlineStr">
+        <is>
+          <t>Northern Rock (UK)</t>
+        </is>
+      </c>
+      <c r="C130" s="16" t="inlineStr">
+        <is>
+          <t>United Kingdom</t>
+        </is>
+      </c>
+      <c r="D130" s="23" t="n">
+        <v>2007</v>
+      </c>
+      <c r="E130" s="16" t="inlineStr">
+        <is>
+          <t>Overexposure to Mortgage Market leading to insolvency</t>
+        </is>
+      </c>
+      <c r="F130" s="16" t="inlineStr">
+        <is>
+          <t>Credit Risk</t>
+        </is>
+      </c>
+      <c r="G130" s="16" t="inlineStr">
+        <is>
+          <t>Strategic</t>
+        </is>
+      </c>
+      <c r="H130" s="16" t="inlineStr">
+        <is>
+          <t>£26 billion</t>
+        </is>
+      </c>
+      <c r="I130" s="34" t="n">
+        <v>35100</v>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" s="35" t="n">
+        <v>126</v>
+      </c>
+      <c r="B131" s="36" t="inlineStr">
+        <is>
+          <t>Olympus Corporation (Japan)</t>
+        </is>
+      </c>
+      <c r="C131" s="36" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="D131" s="35" t="n">
+        <v>2011</v>
+      </c>
+      <c r="E131" s="36" t="inlineStr">
+        <is>
+          <t>Accounting Fraud</t>
+        </is>
+      </c>
+      <c r="F131" s="36" t="inlineStr">
+        <is>
+          <t>Operational Risk</t>
+        </is>
+      </c>
+      <c r="G131" s="36" t="inlineStr">
+        <is>
+          <t>Reporting</t>
+        </is>
+      </c>
+      <c r="H131" s="36" t="inlineStr">
+        <is>
+          <t>$1.7 billion</t>
+        </is>
+      </c>
+      <c r="I131" s="37" t="n">
+        <v>1700</v>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" s="23" t="n">
+        <v>127</v>
+      </c>
+      <c r="B132" s="16" t="inlineStr">
+        <is>
+          <t>Parmalat (Italy)</t>
+        </is>
+      </c>
+      <c r="C132" s="16" t="inlineStr">
+        <is>
+          <t>Italy</t>
+        </is>
+      </c>
+      <c r="D132" s="23" t="n">
+        <v>2003</v>
+      </c>
+      <c r="E132" s="16" t="inlineStr">
+        <is>
+          <t>Accounting Fraud</t>
+        </is>
+      </c>
+      <c r="F132" s="16" t="inlineStr">
+        <is>
+          <t>Operational Risk</t>
+        </is>
+      </c>
+      <c r="G132" s="16" t="inlineStr">
+        <is>
+          <t>Reporting</t>
+        </is>
+      </c>
+      <c r="H132" s="16" t="inlineStr">
+        <is>
+          <t>$20 billion</t>
+        </is>
+      </c>
+      <c r="I132" s="34" t="n">
+        <v>20000</v>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" s="35" t="n">
+        <v>128</v>
+      </c>
+      <c r="B133" s="36" t="inlineStr">
+        <is>
+          <t>Patisserie Valerie (UK)</t>
+        </is>
+      </c>
+      <c r="C133" s="36" t="inlineStr">
+        <is>
+          <t>United Kingdom</t>
+        </is>
+      </c>
+      <c r="D133" s="35" t="n">
+        <v>2018</v>
+      </c>
+      <c r="E133" s="36" t="inlineStr">
+        <is>
+          <t>Accounting Fraud</t>
+        </is>
+      </c>
+      <c r="F133" s="36" t="inlineStr">
+        <is>
+          <t>Operational Risk</t>
+        </is>
+      </c>
+      <c r="G133" s="36" t="inlineStr">
+        <is>
+          <t>Reporting</t>
+        </is>
+      </c>
+      <c r="H133" s="36" t="inlineStr">
+        <is>
+          <t>£94 million</t>
+        </is>
+      </c>
+      <c r="I133" s="37" t="n">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" s="23" t="n">
+        <v>129</v>
+      </c>
+      <c r="B134" s="16" t="inlineStr">
+        <is>
+          <t>PennyMac (US)</t>
+        </is>
+      </c>
+      <c r="C134" s="16" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="D134" s="23" t="n">
+        <v>2008</v>
+      </c>
+      <c r="E134" s="16" t="inlineStr">
+        <is>
+          <t>Subprime Mortgage Lending</t>
+        </is>
+      </c>
+      <c r="F134" s="16" t="inlineStr">
+        <is>
+          <t>Credit Risk</t>
+        </is>
+      </c>
+      <c r="G134" s="16" t="inlineStr">
+        <is>
+          <t>Strategic</t>
+        </is>
+      </c>
+      <c r="H134" s="16" t="inlineStr">
+        <is>
+          <t>$12.2 billion</t>
+        </is>
+      </c>
+      <c r="I134" s="34" t="n">
+        <v>12200</v>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" s="35" t="n">
+        <v>130</v>
+      </c>
+      <c r="B135" s="36" t="inlineStr">
+        <is>
+          <t>Petrobras (Brazil)</t>
+        </is>
+      </c>
+      <c r="C135" s="36" t="inlineStr">
+        <is>
+          <t>Brazil</t>
+        </is>
+      </c>
+      <c r="D135" s="35" t="n">
+        <v>2014</v>
+      </c>
+      <c r="E135" s="36" t="inlineStr">
+        <is>
+          <t>Operation Car Wash (Corruption Scandal)</t>
+        </is>
+      </c>
+      <c r="F135" s="36" t="inlineStr">
+        <is>
+          <t>Operational Risk</t>
+        </is>
+      </c>
+      <c r="G135" s="36" t="inlineStr">
+        <is>
+          <t>Compliance</t>
+        </is>
+      </c>
+      <c r="H135" s="36" t="inlineStr">
+        <is>
+          <t>$2.1 billion</t>
+        </is>
+      </c>
+      <c r="I135" s="37" t="n">
+        <v>2100</v>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" s="23" t="n">
+        <v>131</v>
+      </c>
+      <c r="B136" s="16" t="inlineStr">
+        <is>
+          <t>Pilatus Bank (Malta)</t>
+        </is>
+      </c>
+      <c r="C136" s="16" t="inlineStr">
+        <is>
+          <t>Malta</t>
+        </is>
+      </c>
+      <c r="D136" s="23" t="n">
+        <v>2018</v>
+      </c>
+      <c r="E136" s="16" t="inlineStr">
+        <is>
+          <t>Money Laundering and Fraud</t>
+        </is>
+      </c>
+      <c r="F136" s="16" t="inlineStr">
+        <is>
+          <t>Operational Risk</t>
+        </is>
+      </c>
+      <c r="G136" s="16" t="inlineStr">
+        <is>
+          <t>Compliance</t>
+        </is>
+      </c>
+      <c r="H136" s="16" t="inlineStr">
+        <is>
+          <t>€500 million</t>
+        </is>
+      </c>
+      <c r="I136" s="34" t="n">
+        <v>590</v>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" s="35" t="n">
+        <v>132</v>
+      </c>
+      <c r="B137" s="36" t="inlineStr">
+        <is>
+          <t>Postbank (Ireland)</t>
+        </is>
+      </c>
+      <c r="C137" s="36" t="inlineStr">
+        <is>
+          <t>Ireland</t>
+        </is>
+      </c>
+      <c r="D137" s="35" t="n">
+        <v>2010</v>
+      </c>
+      <c r="E137" s="36" t="inlineStr">
+        <is>
+          <t>Liquidity Crisis leading to insolvency</t>
+        </is>
+      </c>
+      <c r="F137" s="36" t="inlineStr">
+        <is>
+          <t>Liquidity Risk</t>
+        </is>
+      </c>
+      <c r="G137" s="36" t="inlineStr">
+        <is>
+          <t>Strategic</t>
+        </is>
+      </c>
+      <c r="H137" s="36" t="inlineStr">
+        <is>
+          <t>€500 million</t>
+        </is>
+      </c>
+      <c r="I137" s="37" t="n">
+        <v>590</v>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" s="23" t="n">
+        <v>133</v>
+      </c>
+      <c r="B138" s="16" t="inlineStr">
+        <is>
+          <t>PrivatBank (Ukraine)</t>
+        </is>
+      </c>
+      <c r="C138" s="16" t="inlineStr">
+        <is>
+          <t>Ukraine</t>
+        </is>
+      </c>
+      <c r="D138" s="23" t="n">
+        <v>2016</v>
+      </c>
+      <c r="E138" s="16" t="inlineStr">
+        <is>
+          <t>Large-scale Money-laundering</t>
+        </is>
+      </c>
+      <c r="F138" s="16" t="inlineStr">
+        <is>
+          <t>Operational Risk</t>
+        </is>
+      </c>
+      <c r="G138" s="16" t="inlineStr">
+        <is>
+          <t>Compliance</t>
+        </is>
+      </c>
+      <c r="H138" s="16" t="inlineStr">
+        <is>
+          <t>$5.5 billion</t>
+        </is>
+      </c>
+      <c r="I138" s="34" t="n">
+        <v>5500</v>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" s="35" t="n">
+        <v>134</v>
+      </c>
+      <c r="B139" s="36" t="inlineStr">
+        <is>
+          <t>Punjab National Bank (India)</t>
+        </is>
+      </c>
+      <c r="C139" s="36" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="D139" s="35" t="n">
+        <v>2018</v>
+      </c>
+      <c r="E139" s="36" t="inlineStr">
+        <is>
+          <t>Fraudulent Letter of Undertaking Issuance</t>
+        </is>
+      </c>
+      <c r="F139" s="36" t="inlineStr">
+        <is>
+          <t>Operational Risk</t>
+        </is>
+      </c>
+      <c r="G139" s="36" t="inlineStr">
+        <is>
+          <t>Operations</t>
+        </is>
+      </c>
+      <c r="H139" s="36" t="inlineStr">
+        <is>
+          <t>$2 billion</t>
+        </is>
+      </c>
+      <c r="I139" s="37" t="n">
+        <v>2000</v>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" s="23" t="n">
+        <v>135</v>
+      </c>
+      <c r="B140" s="16" t="inlineStr">
+        <is>
+          <t>Punjab National Bank (India)</t>
+        </is>
+      </c>
+      <c r="C140" s="16" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="D140" s="23" t="n">
+        <v>2018</v>
+      </c>
+      <c r="E140" s="16" t="inlineStr">
+        <is>
+          <t>Letter of Undertaking Fraud</t>
+        </is>
+      </c>
+      <c r="F140" s="16" t="inlineStr">
+        <is>
+          <t>Operational Risk</t>
+        </is>
+      </c>
+      <c r="G140" s="16" t="inlineStr">
+        <is>
+          <t>Operations</t>
+        </is>
+      </c>
+      <c r="H140" s="16" t="inlineStr">
+        <is>
+          <t>$1.8 billion</t>
+        </is>
+      </c>
+      <c r="I140" s="34" t="n">
+        <v>1800</v>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" s="35" t="n">
+        <v>136</v>
+      </c>
+      <c r="B141" s="36" t="inlineStr">
+        <is>
+          <t>Rabobank (Netherlands)</t>
+        </is>
+      </c>
+      <c r="C141" s="36" t="inlineStr">
+        <is>
+          <t>Netherlands</t>
+        </is>
+      </c>
+      <c r="D141" s="35" t="n">
+        <v>2013</v>
+      </c>
+      <c r="E141" s="36" t="inlineStr">
+        <is>
+          <t>Libor and Euribor Scandal</t>
+        </is>
+      </c>
+      <c r="F141" s="36" t="inlineStr">
+        <is>
+          <t>Conduct Risk</t>
+        </is>
+      </c>
+      <c r="G141" s="36" t="inlineStr">
+        <is>
+          <t>Compliance</t>
+        </is>
+      </c>
+      <c r="H141" s="36" t="inlineStr">
+        <is>
+          <t>$1 billion</t>
+        </is>
+      </c>
+      <c r="I141" s="37" t="n">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" s="23" t="n">
+        <v>137</v>
+      </c>
+      <c r="B142" s="16" t="inlineStr">
+        <is>
+          <t>Raiffeisen Bank (Austria)</t>
+        </is>
+      </c>
+      <c r="C142" s="16" t="inlineStr">
+        <is>
+          <t>Austria</t>
+        </is>
+      </c>
+      <c r="D142" s="23" t="n">
+        <v>2019</v>
+      </c>
+      <c r="E142" s="16" t="inlineStr">
+        <is>
+          <t>Money Laundering and Corruption Allegations</t>
+        </is>
+      </c>
+      <c r="F142" s="16" t="inlineStr">
+        <is>
+          <t>Operational Risk</t>
+        </is>
+      </c>
+      <c r="G142" s="16" t="inlineStr">
+        <is>
+          <t>Compliance</t>
+        </is>
+      </c>
+      <c r="H142" s="16" t="inlineStr">
+        <is>
+          <t>€5 million</t>
+        </is>
+      </c>
+      <c r="I142" s="34" t="n">
+        <v>5.9</v>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" s="35" t="n">
+        <v>138</v>
+      </c>
+      <c r="B143" s="36" t="inlineStr">
+        <is>
+          <t>Refco</t>
+        </is>
+      </c>
+      <c r="C143" s="36" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="D143" s="35" t="n">
+        <v>2005</v>
+      </c>
+      <c r="E143" s="36" t="inlineStr">
+        <is>
+          <t>Debt Fraud</t>
+        </is>
+      </c>
+      <c r="F143" s="36" t="inlineStr">
+        <is>
+          <t>Operational Risk</t>
+        </is>
+      </c>
+      <c r="G143" s="36" t="inlineStr">
+        <is>
+          <t>Reporting</t>
+        </is>
+      </c>
+      <c r="H143" s="36" t="inlineStr">
+        <is>
+          <t>$2.4 billion</t>
+        </is>
+      </c>
+      <c r="I143" s="37" t="n">
+        <v>2400</v>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" s="23" t="n">
+        <v>139</v>
+      </c>
+      <c r="B144" s="16" t="inlineStr">
+        <is>
+          <t>Roskilde Bank (Denmark)</t>
+        </is>
+      </c>
+      <c r="C144" s="16" t="inlineStr">
+        <is>
+          <t>Denmark</t>
+        </is>
+      </c>
+      <c r="D144" s="23" t="n">
+        <v>2008</v>
+      </c>
+      <c r="E144" s="16" t="inlineStr">
+        <is>
+          <t>Overexposure to Real Estate Market</t>
+        </is>
+      </c>
+      <c r="F144" s="16" t="inlineStr">
+        <is>
+          <t>Credit Risk</t>
+        </is>
+      </c>
+      <c r="G144" s="16" t="inlineStr">
+        <is>
+          <t>Strategic</t>
+        </is>
+      </c>
+      <c r="H144" s="16" t="inlineStr">
+        <is>
+          <t>€1 billion</t>
+        </is>
+      </c>
+      <c r="I144" s="34" t="n">
+        <v>1200</v>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" s="35" t="n">
+        <v>140</v>
+      </c>
+      <c r="B145" s="36" t="inlineStr">
+        <is>
+          <t>Royal Ahold (Netherlands)</t>
+        </is>
+      </c>
+      <c r="C145" s="36" t="inlineStr">
+        <is>
+          <t>Netherlands</t>
+        </is>
+      </c>
+      <c r="D145" s="35" t="n">
+        <v>2003</v>
+      </c>
+      <c r="E145" s="36" t="inlineStr">
+        <is>
+          <t>Accounting Fraud</t>
+        </is>
+      </c>
+      <c r="F145" s="36" t="inlineStr">
+        <is>
+          <t>Operational Risk</t>
+        </is>
+      </c>
+      <c r="G145" s="36" t="inlineStr">
+        <is>
+          <t>Reporting</t>
+        </is>
+      </c>
+      <c r="H145" s="36" t="inlineStr">
+        <is>
+          <t>$1 billion</t>
+        </is>
+      </c>
+      <c r="I145" s="37" t="n">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" s="23" t="n">
+        <v>141</v>
+      </c>
+      <c r="B146" s="16" t="inlineStr">
+        <is>
+          <t>Royal Bank of Scotland (UK)</t>
+        </is>
+      </c>
+      <c r="C146" s="16" t="inlineStr">
+        <is>
+          <t>United Kingdom</t>
+        </is>
+      </c>
+      <c r="D146" s="23" t="n">
+        <v>2008</v>
+      </c>
+      <c r="E146" s="16" t="inlineStr">
+        <is>
+          <t>Overexposure to Subprime Mortgages</t>
+        </is>
+      </c>
+      <c r="F146" s="16" t="inlineStr">
+        <is>
+          <t>Credit Risk</t>
+        </is>
+      </c>
+      <c r="G146" s="16" t="inlineStr">
+        <is>
+          <t>Strategic</t>
+        </is>
+      </c>
+      <c r="H146" s="16" t="inlineStr">
+        <is>
+          <t>£24.1 billion</t>
+        </is>
+      </c>
+      <c r="I146" s="34" t="n">
+        <v>32500</v>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" s="35" t="n">
+        <v>142</v>
+      </c>
+      <c r="B147" s="36" t="inlineStr">
+        <is>
+          <t>Royal Bank of Scotland (UK)</t>
+        </is>
+      </c>
+      <c r="C147" s="36" t="inlineStr">
+        <is>
+          <t>United Kingdom</t>
+        </is>
+      </c>
+      <c r="D147" s="35" t="n">
+        <v>2008</v>
+      </c>
+      <c r="E147" s="36" t="inlineStr">
+        <is>
+          <t>Overexposure to Subprime Mortgage Market leading to nationalization</t>
+        </is>
+      </c>
+      <c r="F147" s="36" t="inlineStr">
+        <is>
+          <t>Credit Risk</t>
+        </is>
+      </c>
+      <c r="G147" s="36" t="inlineStr">
+        <is>
+          <t>Strategic</t>
+        </is>
+      </c>
+      <c r="H147" s="36" t="inlineStr">
+        <is>
+          <t>£45.5 billion</t>
+        </is>
+      </c>
+      <c r="I147" s="37" t="n">
+        <v>61400</v>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" s="23" t="n">
+        <v>143</v>
+      </c>
+      <c r="B148" s="16" t="inlineStr">
+        <is>
+          <t>Royal Bank of Scotland (UK)</t>
+        </is>
+      </c>
+      <c r="C148" s="16" t="inlineStr">
+        <is>
+          <t>United Kingdom</t>
+        </is>
+      </c>
+      <c r="D148" s="23" t="n">
+        <v>2012</v>
+      </c>
+      <c r="E148" s="16" t="inlineStr">
+        <is>
+          <t>IT Systems Failure</t>
+        </is>
+      </c>
+      <c r="F148" s="16" t="inlineStr">
+        <is>
+          <t>Operational Risk</t>
+        </is>
+      </c>
+      <c r="G148" s="16" t="inlineStr">
+        <is>
+          <t>Operations</t>
+        </is>
+      </c>
+      <c r="H148" s="16" t="inlineStr">
+        <is>
+          <t>£175 million</t>
+        </is>
+      </c>
+      <c r="I148" s="34" t="n">
+        <v>236</v>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" s="35" t="n">
+        <v>144</v>
+      </c>
+      <c r="B149" s="36" t="inlineStr">
+        <is>
+          <t>Satyam Computer Services (India)</t>
+        </is>
+      </c>
+      <c r="C149" s="36" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="D149" s="35" t="n">
+        <v>2009</v>
+      </c>
+      <c r="E149" s="36" t="inlineStr">
+        <is>
+          <t>Accounting Fraud</t>
+        </is>
+      </c>
+      <c r="F149" s="36" t="inlineStr">
+        <is>
+          <t>Operational Risk</t>
+        </is>
+      </c>
+      <c r="G149" s="36" t="inlineStr">
+        <is>
+          <t>Reporting</t>
+        </is>
+      </c>
+      <c r="H149" s="36" t="inlineStr">
+        <is>
+          <t>$1.5 billion</t>
+        </is>
+      </c>
+      <c r="I149" s="37" t="n">
+        <v>1500</v>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" s="23" t="n">
+        <v>145</v>
+      </c>
+      <c r="B150" s="16" t="inlineStr">
+        <is>
+          <t>Sino-Forest Corporation (Canada)</t>
+        </is>
+      </c>
+      <c r="C150" s="16" t="inlineStr">
+        <is>
+          <t>Canada</t>
+        </is>
+      </c>
+      <c r="D150" s="23" t="n">
+        <v>2011</v>
+      </c>
+      <c r="E150" s="16" t="inlineStr">
+        <is>
+          <t>Fraud and Misrepresentation</t>
+        </is>
+      </c>
+      <c r="F150" s="16" t="inlineStr">
+        <is>
+          <t>Operational Risk</t>
+        </is>
+      </c>
+      <c r="G150" s="16" t="inlineStr">
+        <is>
+          <t>Reporting</t>
+        </is>
+      </c>
+      <c r="H150" s="16" t="inlineStr">
+        <is>
+          <t>$4 billion CAD</t>
+        </is>
+      </c>
+      <c r="I150" s="34" t="n">
+        <v>4000</v>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" s="35" t="n">
+        <v>146</v>
+      </c>
+      <c r="B151" s="36" t="inlineStr">
+        <is>
+          <t>Skye Bank (Nigeria)</t>
+        </is>
+      </c>
+      <c r="C151" s="36" t="inlineStr">
+        <is>
+          <t>Nigeria</t>
+        </is>
+      </c>
+      <c r="D151" s="35" t="n">
+        <v>2018</v>
+      </c>
+      <c r="E151" s="36" t="inlineStr">
+        <is>
+          <t>Non-performing Loans and Capital Issues</t>
+        </is>
+      </c>
+      <c r="F151" s="36" t="inlineStr">
+        <is>
+          <t>Credit Risk</t>
+        </is>
+      </c>
+      <c r="G151" s="36" t="inlineStr">
+        <is>
+          <t>Operations</t>
+        </is>
+      </c>
+      <c r="H151" s="36" t="inlineStr">
+        <is>
+          <t>$600 million</t>
+        </is>
+      </c>
+      <c r="I151" s="37" t="n">
+        <v>600</v>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" s="23" t="n">
+        <v>147</v>
+      </c>
+      <c r="B152" s="16" t="inlineStr">
+        <is>
+          <t>SNS Reaal (Netherlands)</t>
+        </is>
+      </c>
+      <c r="C152" s="16" t="inlineStr">
+        <is>
+          <t>Netherlands</t>
+        </is>
+      </c>
+      <c r="D152" s="23" t="n">
+        <v>2013</v>
+      </c>
+      <c r="E152" s="16" t="inlineStr">
+        <is>
+          <t>Overexposure to Property Finance</t>
+        </is>
+      </c>
+      <c r="F152" s="16" t="inlineStr">
+        <is>
+          <t>Credit Risk</t>
+        </is>
+      </c>
+      <c r="G152" s="16" t="inlineStr">
+        <is>
+          <t>Strategic</t>
+        </is>
+      </c>
+      <c r="H152" s="16" t="inlineStr">
+        <is>
+          <t>€2.2 billion</t>
+        </is>
+      </c>
+      <c r="I152" s="34" t="n">
+        <v>2600</v>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" s="35" t="n">
+        <v>148</v>
+      </c>
+      <c r="B153" s="36" t="inlineStr">
+        <is>
+          <t>Societe Generale (France)</t>
+        </is>
+      </c>
+      <c r="C153" s="36" t="inlineStr">
+        <is>
+          <t>France</t>
+        </is>
+      </c>
+      <c r="D153" s="35" t="n">
+        <v>2008</v>
+      </c>
+      <c r="E153" s="36" t="inlineStr">
+        <is>
+          <t>Unauthorized Trading (Jerome Kerviel)</t>
+        </is>
+      </c>
+      <c r="F153" s="36" t="inlineStr">
+        <is>
+          <t>Market Risk</t>
+        </is>
+      </c>
+      <c r="G153" s="36" t="inlineStr">
+        <is>
+          <t>Operations</t>
+        </is>
+      </c>
+      <c r="H153" s="36" t="inlineStr">
+        <is>
+          <t>€4.9 billion</t>
+        </is>
+      </c>
+      <c r="I153" s="37" t="n">
+        <v>5800</v>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" s="23" t="n">
+        <v>149</v>
+      </c>
+      <c r="B154" s="16" t="inlineStr">
+        <is>
+          <t>Societe Generale (France)</t>
+        </is>
+      </c>
+      <c r="C154" s="16" t="inlineStr">
+        <is>
+          <t>France</t>
+        </is>
+      </c>
+      <c r="D154" s="23" t="n">
+        <v>2018</v>
+      </c>
+      <c r="E154" s="16" t="inlineStr">
+        <is>
+          <t>Libor and Euribor Scandal</t>
+        </is>
+      </c>
+      <c r="F154" s="16" t="inlineStr">
+        <is>
+          <t>Conduct Risk</t>
+        </is>
+      </c>
+      <c r="G154" s="16" t="inlineStr">
+        <is>
+          <t>Compliance</t>
+        </is>
+      </c>
+      <c r="H154" s="16" t="inlineStr">
+        <is>
+          <t>$1.34 billion</t>
+        </is>
+      </c>
+      <c r="I154" s="34" t="n">
+        <v>1300</v>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" s="35" t="n">
+        <v>150</v>
+      </c>
+      <c r="B155" s="36" t="inlineStr">
+        <is>
+          <t>Standard Chartered (UK)</t>
+        </is>
+      </c>
+      <c r="C155" s="36" t="inlineStr">
+        <is>
+          <t>United Kingdom</t>
+        </is>
+      </c>
+      <c r="D155" s="35" t="n">
+        <v>2012</v>
+      </c>
+      <c r="E155" s="36" t="inlineStr">
+        <is>
+          <t>Sanctions Breaching</t>
+        </is>
+      </c>
+      <c r="F155" s="36" t="inlineStr">
+        <is>
+          <t>Operational Risk</t>
+        </is>
+      </c>
+      <c r="G155" s="36" t="inlineStr">
+        <is>
+          <t>Compliance</t>
+        </is>
+      </c>
+      <c r="H155" s="36" t="inlineStr">
+        <is>
+          <t>$667 million</t>
+        </is>
+      </c>
+      <c r="I155" s="37" t="n">
+        <v>667</v>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" s="23" t="n">
+        <v>151</v>
+      </c>
+      <c r="B156" s="16" t="inlineStr">
+        <is>
+          <t>Stanford Financial Group</t>
+        </is>
+      </c>
+      <c r="C156" s="16" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="D156" s="23" t="n">
+        <v>2009</v>
+      </c>
+      <c r="E156" s="16" t="inlineStr">
+        <is>
+          <t>Ponzi Scheme</t>
+        </is>
+      </c>
+      <c r="F156" s="16" t="inlineStr">
+        <is>
+          <t>Operational Risk</t>
+        </is>
+      </c>
+      <c r="G156" s="16" t="inlineStr">
+        <is>
+          <t>Compliance</t>
+        </is>
+      </c>
+      <c r="H156" s="16" t="inlineStr">
+        <is>
+          <t>$7 billion</t>
+        </is>
+      </c>
+      <c r="I156" s="34" t="n">
+        <v>7000</v>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" s="35" t="n">
+        <v>152</v>
+      </c>
+      <c r="B157" s="36" t="inlineStr">
+        <is>
+          <t>Steinhoff International (South Africa)</t>
+        </is>
+      </c>
+      <c r="C157" s="36" t="inlineStr">
+        <is>
+          <t>South Africa</t>
+        </is>
+      </c>
+      <c r="D157" s="35" t="n">
+        <v>2017</v>
+      </c>
+      <c r="E157" s="36" t="inlineStr">
+        <is>
+          <t>Accounting Fraud</t>
+        </is>
+      </c>
+      <c r="F157" s="36" t="inlineStr">
+        <is>
+          <t>Operational Risk</t>
+        </is>
+      </c>
+      <c r="G157" s="36" t="inlineStr">
+        <is>
+          <t>Reporting</t>
+        </is>
+      </c>
+      <c r="H157" s="36" t="inlineStr">
+        <is>
+          <t>€6 billion</t>
+        </is>
+      </c>
+      <c r="I157" s="37" t="n">
+        <v>7100</v>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" s="23" t="n">
+        <v>153</v>
+      </c>
+      <c r="B158" s="16" t="inlineStr">
+        <is>
+          <t>Steinhoff International (South Africa)</t>
+        </is>
+      </c>
+      <c r="C158" s="16" t="inlineStr">
+        <is>
+          <t>South Africa</t>
+        </is>
+      </c>
+      <c r="D158" s="23" t="n">
+        <v>2017</v>
+      </c>
+      <c r="E158" s="16" t="inlineStr">
+        <is>
+          <t>Accounting Fraud</t>
+        </is>
+      </c>
+      <c r="F158" s="16" t="inlineStr">
+        <is>
+          <t>Operational Risk</t>
+        </is>
+      </c>
+      <c r="G158" s="16" t="inlineStr">
+        <is>
+          <t>Reporting</t>
+        </is>
+      </c>
+      <c r="H158" s="16" t="inlineStr">
+        <is>
+          <t>$7.4 billion</t>
+        </is>
+      </c>
+      <c r="I158" s="34" t="n">
+        <v>7400</v>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" s="35" t="n">
+        <v>154</v>
+      </c>
+      <c r="B159" s="36" t="inlineStr">
+        <is>
+          <t>Swedbank (Sweden)</t>
+        </is>
+      </c>
+      <c r="C159" s="36" t="inlineStr">
+        <is>
+          <t>Sweden</t>
+        </is>
+      </c>
+      <c r="D159" s="35" t="n">
+        <v>2019</v>
+      </c>
+      <c r="E159" s="36" t="inlineStr">
+        <is>
+          <t>Money Laundering</t>
+        </is>
+      </c>
+      <c r="F159" s="36" t="inlineStr">
+        <is>
+          <t>Operational Risk</t>
+        </is>
+      </c>
+      <c r="G159" s="36" t="inlineStr">
+        <is>
+          <t>Compliance</t>
+        </is>
+      </c>
+      <c r="H159" s="36" t="inlineStr">
+        <is>
+          <t>SEK 4 billion</t>
+        </is>
+      </c>
+      <c r="I159" s="37" t="n">
+        <v>440</v>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" s="23" t="n">
+        <v>155</v>
+      </c>
+      <c r="B160" s="16" t="inlineStr">
+        <is>
+          <t>Tatfondbank (Russia)</t>
+        </is>
+      </c>
+      <c r="C160" s="16" t="inlineStr">
+        <is>
+          <t>Russia</t>
+        </is>
+      </c>
+      <c r="D160" s="23" t="n">
+        <v>2017</v>
+      </c>
+      <c r="E160" s="16" t="inlineStr">
+        <is>
+          <t>Misappropriation of Funds</t>
+        </is>
+      </c>
+      <c r="F160" s="16" t="inlineStr">
+        <is>
+          <t>Operational Risk</t>
+        </is>
+      </c>
+      <c r="G160" s="16" t="inlineStr">
+        <is>
+          <t>Operations</t>
+        </is>
+      </c>
+      <c r="H160" s="16" t="inlineStr">
+        <is>
+          <t>RUB 97 billion</t>
+        </is>
+      </c>
+      <c r="I160" s="34" t="n">
+        <v>1300</v>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" s="35" t="n">
+        <v>156</v>
+      </c>
+      <c r="B161" s="36" t="inlineStr">
+        <is>
+          <t>Tesco Bank (UK)</t>
+        </is>
+      </c>
+      <c r="C161" s="36" t="inlineStr">
+        <is>
+          <t>United Kingdom</t>
+        </is>
+      </c>
+      <c r="D161" s="35" t="n">
+        <v>2016</v>
+      </c>
+      <c r="E161" s="36" t="inlineStr">
+        <is>
+          <t>Cyber Attack leading to account balance theft</t>
+        </is>
+      </c>
+      <c r="F161" s="36" t="inlineStr">
+        <is>
+          <t>Operational Risk</t>
+        </is>
+      </c>
+      <c r="G161" s="36" t="inlineStr">
+        <is>
+          <t>Operations</t>
+        </is>
+      </c>
+      <c r="H161" s="36" t="inlineStr">
+        <is>
+          <t>£2.5 million</t>
+        </is>
+      </c>
+      <c r="I161" s="37" t="n">
+        <v>3.4</v>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" s="23" t="n">
+        <v>157</v>
+      </c>
+      <c r="B162" s="16" t="inlineStr">
+        <is>
+          <t>Toshiba (Japan)</t>
+        </is>
+      </c>
+      <c r="C162" s="16" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="D162" s="23" t="n">
+        <v>2015</v>
+      </c>
+      <c r="E162" s="16" t="inlineStr">
+        <is>
+          <t>Accounting Fraud</t>
+        </is>
+      </c>
+      <c r="F162" s="16" t="inlineStr">
+        <is>
+          <t>Operational Risk</t>
+        </is>
+      </c>
+      <c r="G162" s="16" t="inlineStr">
+        <is>
+          <t>Reporting</t>
+        </is>
+      </c>
+      <c r="H162" s="16" t="inlineStr">
+        <is>
+          <t>$1.2 billion</t>
+        </is>
+      </c>
+      <c r="I162" s="34" t="n">
+        <v>1200</v>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" s="35" t="n">
+        <v>158</v>
+      </c>
+      <c r="B163" s="36" t="inlineStr">
+        <is>
+          <t>Tyco International</t>
+        </is>
+      </c>
+      <c r="C163" s="36" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="D163" s="35" t="n">
+        <v>2002</v>
+      </c>
+      <c r="E163" s="36" t="inlineStr">
+        <is>
+          <t>Financial Fraud by Executives</t>
+        </is>
+      </c>
+      <c r="F163" s="36" t="inlineStr">
+        <is>
+          <t>Operational Risk</t>
+        </is>
+      </c>
+      <c r="G163" s="36" t="inlineStr">
+        <is>
+          <t>Operations</t>
+        </is>
+      </c>
+      <c r="H163" s="36" t="inlineStr">
+        <is>
+          <t>$3.2 billion</t>
+        </is>
+      </c>
+      <c r="I163" s="37" t="n">
+        <v>3200</v>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" s="23" t="n">
+        <v>159</v>
+      </c>
+      <c r="B164" s="16" t="inlineStr">
+        <is>
+          <t>UBS (Switzerland)</t>
+        </is>
+      </c>
+      <c r="C164" s="16" t="inlineStr">
+        <is>
+          <t>Switzerland</t>
+        </is>
+      </c>
+      <c r="D164" s="23" t="n">
+        <v>2008</v>
+      </c>
+      <c r="E164" s="16" t="inlineStr">
+        <is>
+          <t>Overexposure to Subprime Mortgages</t>
+        </is>
+      </c>
+      <c r="F164" s="16" t="inlineStr">
+        <is>
+          <t>Credit Risk</t>
+        </is>
+      </c>
+      <c r="G164" s="16" t="inlineStr">
+        <is>
+          <t>Strategic</t>
+        </is>
+      </c>
+      <c r="H164" s="16" t="inlineStr">
+        <is>
+          <t>$37.4 billion</t>
+        </is>
+      </c>
+      <c r="I164" s="34" t="n">
+        <v>37400</v>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" s="35" t="n">
+        <v>160</v>
+      </c>
+      <c r="B165" s="36" t="inlineStr">
+        <is>
+          <t>UBS (Switzerland)</t>
+        </is>
+      </c>
+      <c r="C165" s="36" t="inlineStr">
+        <is>
+          <t>Switzerland</t>
+        </is>
+      </c>
+      <c r="D165" s="35" t="n">
+        <v>2008</v>
+      </c>
+      <c r="E165" s="36" t="inlineStr">
+        <is>
+          <t>Overexposure to Subprime Mortgage Market leading to insolvency</t>
+        </is>
+      </c>
+      <c r="F165" s="36" t="inlineStr">
+        <is>
+          <t>Credit Risk</t>
+        </is>
+      </c>
+      <c r="G165" s="36" t="inlineStr">
+        <is>
+          <t>Strategic</t>
+        </is>
+      </c>
+      <c r="H165" s="36" t="inlineStr">
+        <is>
+          <t>$21.34 billion</t>
+        </is>
+      </c>
+      <c r="I165" s="37" t="n">
+        <v>21300</v>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" s="23" t="n">
+        <v>161</v>
+      </c>
+      <c r="B166" s="16" t="inlineStr">
+        <is>
+          <t>UBS (Switzerland)</t>
+        </is>
+      </c>
+      <c r="C166" s="16" t="inlineStr">
+        <is>
+          <t>Switzerland</t>
+        </is>
+      </c>
+      <c r="D166" s="23" t="n">
+        <v>2011</v>
+      </c>
+      <c r="E166" s="16" t="inlineStr">
+        <is>
+          <t>Unauthorized Trading</t>
+        </is>
+      </c>
+      <c r="F166" s="16" t="inlineStr">
+        <is>
+          <t>Market Risk</t>
+        </is>
+      </c>
+      <c r="G166" s="16" t="inlineStr">
+        <is>
+          <t>Operations</t>
+        </is>
+      </c>
+      <c r="H166" s="16" t="inlineStr">
+        <is>
+          <t>$2.3 billion</t>
+        </is>
+      </c>
+      <c r="I166" s="34" t="n">
+        <v>2300</v>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" s="35" t="n">
+        <v>162</v>
+      </c>
+      <c r="B167" s="36" t="inlineStr">
+        <is>
+          <t>UBS (Switzerland)</t>
+        </is>
+      </c>
+      <c r="C167" s="36" t="inlineStr">
+        <is>
+          <t>Switzerland</t>
+        </is>
+      </c>
+      <c r="D167" s="35" t="n">
+        <v>2013</v>
+      </c>
+      <c r="E167" s="36" t="inlineStr">
+        <is>
+          <t>Unauthorized Trading</t>
+        </is>
+      </c>
+      <c r="F167" s="36" t="inlineStr">
+        <is>
+          <t>Market Risk</t>
+        </is>
+      </c>
+      <c r="G167" s="36" t="inlineStr">
+        <is>
+          <t>Operations</t>
+        </is>
+      </c>
+      <c r="H167" s="36" t="inlineStr">
+        <is>
+          <t>CHF 2.2 billion</t>
+        </is>
+      </c>
+      <c r="I167" s="37" t="n">
+        <v>2400</v>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" s="23" t="n">
+        <v>163</v>
+      </c>
+      <c r="B168" s="16" t="inlineStr">
+        <is>
+          <t>UBS (Switzerland)</t>
+        </is>
+      </c>
+      <c r="C168" s="16" t="inlineStr">
+        <is>
+          <t>Switzerland</t>
+        </is>
+      </c>
+      <c r="D168" s="23" t="n">
+        <v>2019</v>
+      </c>
+      <c r="E168" s="16" t="inlineStr">
+        <is>
+          <t>Tax Evasion</t>
+        </is>
+      </c>
+      <c r="F168" s="16" t="inlineStr">
+        <is>
+          <t>Conduct Risk</t>
+        </is>
+      </c>
+      <c r="G168" s="16" t="inlineStr">
+        <is>
+          <t>Compliance</t>
+        </is>
+      </c>
+      <c r="H168" s="16" t="inlineStr">
+        <is>
+          <t>€4.5 billion</t>
+        </is>
+      </c>
+      <c r="I168" s="34" t="n">
+        <v>5300</v>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" s="35" t="n">
+        <v>164</v>
+      </c>
+      <c r="B169" s="36" t="inlineStr">
+        <is>
+          <t>UBS AG (Switzerland)</t>
+        </is>
+      </c>
+      <c r="C169" s="36" t="inlineStr">
+        <is>
+          <t>Switzerland</t>
+        </is>
+      </c>
+      <c r="D169" s="35" t="n">
+        <v>2012</v>
+      </c>
+      <c r="E169" s="36" t="inlineStr">
+        <is>
+          <t>Unauthorized Trading</t>
+        </is>
+      </c>
+      <c r="F169" s="36" t="inlineStr">
+        <is>
+          <t>Market Risk</t>
+        </is>
+      </c>
+      <c r="G169" s="36" t="inlineStr">
+        <is>
+          <t>Operations</t>
+        </is>
+      </c>
+      <c r="H169" s="36" t="inlineStr">
+        <is>
+          <t>$2.3 billion</t>
+        </is>
+      </c>
+      <c r="I169" s="37" t="n">
+        <v>2300</v>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" s="23" t="n">
+        <v>165</v>
+      </c>
+      <c r="B170" s="16" t="inlineStr">
+        <is>
+          <t>UniCredit (Italy)</t>
+        </is>
+      </c>
+      <c r="C170" s="16" t="inlineStr">
+        <is>
+          <t>Italy</t>
+        </is>
+      </c>
+      <c r="D170" s="23" t="n">
+        <v>2008</v>
+      </c>
+      <c r="E170" s="16" t="inlineStr">
+        <is>
+          <t>Overexposure to Subprime Mortgages</t>
+        </is>
+      </c>
+      <c r="F170" s="16" t="inlineStr">
+        <is>
+          <t>Credit Risk</t>
+        </is>
+      </c>
+      <c r="G170" s="16" t="inlineStr">
+        <is>
+          <t>Strategic</t>
+        </is>
+      </c>
+      <c r="H170" s="16" t="inlineStr">
+        <is>
+          <t>$19.2 billion</t>
+        </is>
+      </c>
+      <c r="I170" s="34" t="n">
+        <v>19200</v>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" s="35" t="n">
+        <v>166</v>
+      </c>
+      <c r="B171" s="36" t="inlineStr">
+        <is>
+          <t>VBS Mutual Bank (South Africa)</t>
+        </is>
+      </c>
+      <c r="C171" s="36" t="inlineStr">
+        <is>
+          <t>South Africa</t>
+        </is>
+      </c>
+      <c r="D171" s="35" t="n">
+        <v>2018</v>
+      </c>
+      <c r="E171" s="36" t="inlineStr">
+        <is>
+          <t>Looting and Fraud</t>
+        </is>
+      </c>
+      <c r="F171" s="36" t="inlineStr">
+        <is>
+          <t>Operational Risk</t>
+        </is>
+      </c>
+      <c r="G171" s="36" t="inlineStr">
+        <is>
+          <t>Operations</t>
+        </is>
+      </c>
+      <c r="H171" s="36" t="inlineStr">
+        <is>
+          <t>R2 billion</t>
+        </is>
+      </c>
+      <c r="I171" s="37" t="n">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" s="23" t="n">
+        <v>167</v>
+      </c>
+      <c r="B172" s="16" t="inlineStr">
+        <is>
+          <t>Veneto Banca (Italy)</t>
+        </is>
+      </c>
+      <c r="C172" s="16" t="inlineStr">
+        <is>
+          <t>Italy</t>
+        </is>
+      </c>
+      <c r="D172" s="23" t="n">
+        <v>2017</v>
+      </c>
+      <c r="E172" s="16" t="inlineStr">
+        <is>
+          <t>Fraud and Mismanagement</t>
+        </is>
+      </c>
+      <c r="F172" s="16" t="inlineStr">
+        <is>
+          <t>Operational Risk</t>
+        </is>
+      </c>
+      <c r="G172" s="16" t="inlineStr">
+        <is>
+          <t>Reporting</t>
+        </is>
+      </c>
+      <c r="H172" s="16" t="inlineStr">
+        <is>
+          <t>€10 billion</t>
+        </is>
+      </c>
+      <c r="I172" s="34" t="n">
+        <v>11800</v>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" s="35" t="n">
+        <v>168</v>
+      </c>
+      <c r="B173" s="36" t="inlineStr">
+        <is>
+          <t>Visa (US)</t>
+        </is>
+      </c>
+      <c r="C173" s="36" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="D173" s="35" t="n">
+        <v>2019</v>
+      </c>
+      <c r="E173" s="36" t="inlineStr">
+        <is>
+          <t>System Failure leading to transaction disruptions</t>
+        </is>
+      </c>
+      <c r="F173" s="36" t="inlineStr">
+        <is>
+          <t>Operational Risk</t>
+        </is>
+      </c>
+      <c r="G173" s="36" t="inlineStr">
+        <is>
+          <t>Operations</t>
+        </is>
+      </c>
+      <c r="H173" s="36" t="inlineStr">
+        <is>
+          <t>$1.2 billion</t>
+        </is>
+      </c>
+      <c r="I173" s="37" t="n">
+        <v>1200</v>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" s="23" t="n">
+        <v>169</v>
+      </c>
+      <c r="B174" s="16" t="inlineStr">
+        <is>
+          <t>Vivendi</t>
+        </is>
+      </c>
+      <c r="C174" s="16" t="inlineStr">
+        <is>
+          <t>France</t>
+        </is>
+      </c>
+      <c r="D174" s="23" t="n">
+        <v>2002</v>
+      </c>
+      <c r="E174" s="16" t="inlineStr">
+        <is>
+          <t>Accounting Fraud</t>
+        </is>
+      </c>
+      <c r="F174" s="16" t="inlineStr">
+        <is>
+          <t>Operational Risk</t>
+        </is>
+      </c>
+      <c r="G174" s="16" t="inlineStr">
+        <is>
+          <t>Reporting</t>
+        </is>
+      </c>
+      <c r="H174" s="16" t="inlineStr">
+        <is>
+          <t>€3.1 billion</t>
+        </is>
+      </c>
+      <c r="I174" s="34" t="n">
+        <v>3700</v>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" s="35" t="n">
+        <v>170</v>
+      </c>
+      <c r="B175" s="36" t="inlineStr">
+        <is>
+          <t>Wachovia (US)</t>
+        </is>
+      </c>
+      <c r="C175" s="36" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="D175" s="35" t="n">
+        <v>2008</v>
+      </c>
+      <c r="E175" s="36" t="inlineStr">
+        <is>
+          <t>Overexposure to Subprime Mortgage Market leading to insolvency</t>
+        </is>
+      </c>
+      <c r="F175" s="36" t="inlineStr">
+        <is>
+          <t>Credit Risk</t>
+        </is>
+      </c>
+      <c r="G175" s="36" t="inlineStr">
+        <is>
+          <t>Strategic</t>
+        </is>
+      </c>
+      <c r="H175" s="36" t="inlineStr">
+        <is>
+          <t>$25 billion</t>
+        </is>
+      </c>
+      <c r="I175" s="37" t="n">
+        <v>25000</v>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" s="23" t="n">
+        <v>171</v>
+      </c>
+      <c r="B176" s="16" t="inlineStr">
+        <is>
+          <t>Washington Mutual</t>
+        </is>
+      </c>
+      <c r="C176" s="16" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="D176" s="23" t="n">
+        <v>2008</v>
+      </c>
+      <c r="E176" s="16" t="inlineStr">
+        <is>
+          <t>Overexposure to Mortgage Lending</t>
+        </is>
+      </c>
+      <c r="F176" s="16" t="inlineStr">
+        <is>
+          <t>Credit Risk</t>
+        </is>
+      </c>
+      <c r="G176" s="16" t="inlineStr">
+        <is>
+          <t>Strategic</t>
+        </is>
+      </c>
+      <c r="H176" s="16" t="inlineStr">
+        <is>
+          <t>$31.8 billion</t>
+        </is>
+      </c>
+      <c r="I176" s="34" t="n">
+        <v>31800</v>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177" s="35" t="n">
+        <v>172</v>
+      </c>
+      <c r="B177" s="36" t="inlineStr">
+        <is>
+          <t>Washington Mutual (US)</t>
+        </is>
+      </c>
+      <c r="C177" s="36" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="D177" s="35" t="n">
+        <v>2008</v>
+      </c>
+      <c r="E177" s="36" t="inlineStr">
+        <is>
+          <t>Overexposure to Subprime Mortgage Market leading to insolvency</t>
+        </is>
+      </c>
+      <c r="F177" s="36" t="inlineStr">
+        <is>
+          <t>Credit Risk</t>
+        </is>
+      </c>
+      <c r="G177" s="36" t="inlineStr">
+        <is>
+          <t>Strategic</t>
+        </is>
+      </c>
+      <c r="H177" s="36" t="inlineStr">
+        <is>
+          <t>$16.7 billion</t>
+        </is>
+      </c>
+      <c r="I177" s="37" t="n">
+        <v>16700</v>
+      </c>
+    </row>
+    <row r="178">
+      <c r="A178" s="23" t="n">
+        <v>173</v>
+      </c>
+      <c r="B178" s="16" t="inlineStr">
+        <is>
+          <t>Wells Fargo (US)</t>
+        </is>
+      </c>
+      <c r="C178" s="16" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="D178" s="23" t="n">
+        <v>2016</v>
+      </c>
+      <c r="E178" s="16" t="inlineStr">
+        <is>
+          <t>Fake Accounts Scandal</t>
+        </is>
+      </c>
+      <c r="F178" s="16" t="inlineStr">
+        <is>
+          <t>Conduct Risk</t>
+        </is>
+      </c>
+      <c r="G178" s="16" t="inlineStr">
+        <is>
+          <t>Operations</t>
+        </is>
+      </c>
+      <c r="H178" s="16" t="inlineStr">
+        <is>
+          <t>$3 billion</t>
+        </is>
+      </c>
+      <c r="I178" s="34" t="n">
+        <v>3000</v>
+      </c>
+    </row>
+    <row r="179">
+      <c r="A179" s="35" t="n">
+        <v>174</v>
+      </c>
+      <c r="B179" s="36" t="inlineStr">
+        <is>
+          <t>WestLB (Germany)</t>
+        </is>
+      </c>
+      <c r="C179" s="36" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="D179" s="35" t="n">
+        <v>2008</v>
+      </c>
+      <c r="E179" s="36" t="inlineStr">
+        <is>
+          <t>Overexposure to Subprime Mortgages</t>
+        </is>
+      </c>
+      <c r="F179" s="36" t="inlineStr">
+        <is>
+          <t>Credit Risk</t>
+        </is>
+      </c>
+      <c r="G179" s="36" t="inlineStr">
+        <is>
+          <t>Strategic</t>
+        </is>
+      </c>
+      <c r="H179" s="36" t="inlineStr">
+        <is>
+          <t>€3 billion</t>
+        </is>
+      </c>
+      <c r="I179" s="37" t="n">
+        <v>3500</v>
+      </c>
+    </row>
+    <row r="180">
+      <c r="A180" s="23" t="n">
+        <v>175</v>
+      </c>
+      <c r="B180" s="16" t="inlineStr">
+        <is>
+          <t>WestLB (Germany)</t>
+        </is>
+      </c>
+      <c r="C180" s="16" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="D180" s="23" t="n">
+        <v>2012</v>
+      </c>
+      <c r="E180" s="16" t="inlineStr">
+        <is>
+          <t>Structured Investment Vehicle failure leading to insolvency</t>
+        </is>
+      </c>
+      <c r="F180" s="16" t="inlineStr">
+        <is>
+          <t>Liquidity Risk</t>
+        </is>
+      </c>
+      <c r="G180" s="16" t="inlineStr">
+        <is>
+          <t>Strategic</t>
+        </is>
+      </c>
+      <c r="H180" s="16" t="inlineStr">
+        <is>
+          <t>€18 billion</t>
+        </is>
+      </c>
+      <c r="I180" s="34" t="n">
+        <v>21200</v>
+      </c>
+    </row>
+    <row r="181">
+      <c r="A181" s="35" t="n">
+        <v>176</v>
+      </c>
+      <c r="B181" s="36" t="inlineStr">
+        <is>
+          <t>Westpac (Australia)</t>
+        </is>
+      </c>
+      <c r="C181" s="36" t="inlineStr">
+        <is>
+          <t>Australia</t>
+        </is>
+      </c>
+      <c r="D181" s="35" t="n">
+        <v>2019</v>
+      </c>
+      <c r="E181" s="36" t="inlineStr">
+        <is>
+          <t>Money Laundering and Child Exploitation Scandal</t>
+        </is>
+      </c>
+      <c r="F181" s="36" t="inlineStr">
+        <is>
+          <t>Operational Risk</t>
+        </is>
+      </c>
+      <c r="G181" s="36" t="inlineStr">
+        <is>
+          <t>Compliance</t>
+        </is>
+      </c>
+      <c r="H181" s="36" t="inlineStr">
+        <is>
+          <t>AUD 1.3 billion</t>
+        </is>
+      </c>
+      <c r="I181" s="37" t="n">
+        <v>936</v>
+      </c>
+    </row>
+    <row r="182">
+      <c r="A182" s="23" t="n">
+        <v>177</v>
+      </c>
+      <c r="B182" s="16" t="inlineStr">
+        <is>
+          <t>Wirecard (Germany)</t>
+        </is>
+      </c>
+      <c r="C182" s="16" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="D182" s="23" t="n">
+        <v>2020</v>
+      </c>
+      <c r="E182" s="16" t="inlineStr">
+        <is>
+          <t>Accounting Fraud</t>
+        </is>
+      </c>
+      <c r="F182" s="16" t="inlineStr">
+        <is>
+          <t>Operational Risk</t>
+        </is>
+      </c>
+      <c r="G182" s="16" t="inlineStr">
+        <is>
+          <t>Reporting</t>
+        </is>
+      </c>
+      <c r="H182" s="16" t="inlineStr">
+        <is>
+          <t>€1.9 billion</t>
+        </is>
+      </c>
+      <c r="I182" s="34" t="n">
+        <v>2200</v>
+      </c>
+    </row>
+    <row r="183">
+      <c r="A183" s="35" t="n">
+        <v>178</v>
+      </c>
+      <c r="B183" s="36" t="inlineStr">
+        <is>
+          <t>WorldCom</t>
+        </is>
+      </c>
+      <c r="C183" s="36" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="D183" s="35" t="n">
+        <v>2002</v>
+      </c>
+      <c r="E183" s="36" t="inlineStr">
+        <is>
+          <t>Accounting Fraud</t>
+        </is>
+      </c>
+      <c r="F183" s="36" t="inlineStr">
+        <is>
+          <t>Operational Risk</t>
+        </is>
+      </c>
+      <c r="G183" s="36" t="inlineStr">
+        <is>
+          <t>Reporting</t>
+        </is>
+      </c>
+      <c r="H183" s="36" t="inlineStr">
+        <is>
+          <t>$180 billion</t>
+        </is>
+      </c>
+      <c r="I183" s="37" t="n">
+        <v>180000</v>
+      </c>
+    </row>
+    <row r="184">
+      <c r="A184" s="23" t="n">
+        <v>179</v>
+      </c>
+      <c r="B184" s="16" t="inlineStr">
+        <is>
+          <t>Yes Bank (India)</t>
+        </is>
+      </c>
+      <c r="C184" s="16" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="D184" s="23" t="n">
+        <v>2020</v>
+      </c>
+      <c r="E184" s="16" t="inlineStr">
+        <is>
+          <t>Overexposure to Infrastructure Loans</t>
+        </is>
+      </c>
+      <c r="F184" s="16" t="inlineStr">
+        <is>
+          <t>Credit Risk</t>
+        </is>
+      </c>
+      <c r="G184" s="16" t="inlineStr">
+        <is>
+          <t>Strategic</t>
+        </is>
+      </c>
+      <c r="H184" s="16" t="inlineStr">
+        <is>
+          <t>$2 billion</t>
+        </is>
+      </c>
+      <c r="I184" s="34" t="n">
+        <v>2000</v>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A5:I184"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
